--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E83A45-F013-408C-99EB-E0364BEECBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9420" yWindow="5050" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="212">
   <si>
     <t>lang_code</t>
   </si>
@@ -631,6 +631,39 @@
   </si>
   <si>
     <t>ប្រទេស</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>Utopia</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>UTO/CEN</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>UTO/CEN/FOR</t>
+  </si>
+  <si>
+    <t>CAP</t>
+  </si>
+  <si>
+    <t>Captial</t>
+  </si>
+  <si>
+    <t>UTO/CEN/FOR/CAP</t>
   </si>
 </sst>
 </file>
@@ -1098,17 +1131,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H153"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="2"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1157,7 +1190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1180,7 +1213,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1232,7 +1265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1258,7 +1291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1284,7 +1317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1310,7 +1343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1336,7 +1369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1395,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1388,7 +1421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1414,7 +1447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1440,7 +1473,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1466,7 +1499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1492,7 +1525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -1518,7 +1551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1544,7 +1577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1596,7 +1629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1622,7 +1655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1648,7 +1681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1674,7 +1707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1700,7 +1733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1726,7 +1759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1752,7 +1785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1778,7 +1811,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1804,7 +1837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1830,7 +1863,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1856,7 +1889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1882,7 +1915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1908,7 +1941,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1934,7 +1967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1960,7 +1993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1986,7 +2019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2012,7 +2045,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -2038,7 +2071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2064,7 +2097,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2090,7 +2123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2116,7 +2149,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2142,7 +2175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2168,7 +2201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -2194,7 +2227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2220,7 +2253,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -2243,7 +2276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -2269,7 +2302,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2295,7 +2328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -2321,7 +2354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -2347,7 +2380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>86</v>
       </c>
@@ -2373,7 +2406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>86</v>
       </c>
@@ -2399,7 +2432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -2425,7 +2458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>86</v>
       </c>
@@ -2451,7 +2484,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>86</v>
       </c>
@@ -2477,7 +2510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>86</v>
       </c>
@@ -2503,7 +2536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>86</v>
       </c>
@@ -2529,7 +2562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -2555,7 +2588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -2581,7 +2614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2607,7 +2640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -2633,7 +2666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -2659,7 +2692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>86</v>
       </c>
@@ -2685,7 +2718,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>86</v>
       </c>
@@ -2711,7 +2744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>86</v>
       </c>
@@ -2737,7 +2770,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -2763,7 +2796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>112</v>
       </c>
@@ -2786,7 +2819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>112</v>
       </c>
@@ -2812,7 +2845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>112</v>
       </c>
@@ -2838,7 +2871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -2864,7 +2897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>112</v>
       </c>
@@ -2890,7 +2923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -2916,7 +2949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>112</v>
       </c>
@@ -2942,7 +2975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>112</v>
       </c>
@@ -2968,7 +3001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>112</v>
       </c>
@@ -2994,7 +3027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>112</v>
       </c>
@@ -3020,7 +3053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>112</v>
       </c>
@@ -3046,7 +3079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -3072,7 +3105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -3098,7 +3131,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>112</v>
       </c>
@@ -3124,7 +3157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -3150,7 +3183,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>112</v>
       </c>
@@ -3176,7 +3209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -3202,7 +3235,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3228,7 +3261,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>112</v>
       </c>
@@ -3254,7 +3287,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -3280,7 +3313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -3306,7 +3339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>140</v>
       </c>
@@ -3329,7 +3362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -3355,7 +3388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>140</v>
       </c>
@@ -3381,7 +3414,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>140</v>
       </c>
@@ -3407,7 +3440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>140</v>
       </c>
@@ -3433,7 +3466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>140</v>
       </c>
@@ -3459,7 +3492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>140</v>
       </c>
@@ -3485,7 +3518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>140</v>
       </c>
@@ -3511,7 +3544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>140</v>
       </c>
@@ -3537,7 +3570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>140</v>
       </c>
@@ -3563,7 +3596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>140</v>
       </c>
@@ -3589,7 +3622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>140</v>
       </c>
@@ -3615,7 +3648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>140</v>
       </c>
@@ -3641,7 +3674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>140</v>
       </c>
@@ -3667,7 +3700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3693,7 +3726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>140</v>
       </c>
@@ -3719,7 +3752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>140</v>
       </c>
@@ -3745,7 +3778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>140</v>
       </c>
@@ -3771,7 +3804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -3797,7 +3830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -3823,7 +3856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>140</v>
       </c>
@@ -3849,7 +3882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>167</v>
       </c>
@@ -3872,7 +3905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>167</v>
       </c>
@@ -3898,7 +3931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>167</v>
       </c>
@@ -3924,7 +3957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>167</v>
       </c>
@@ -3950,7 +3983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>167</v>
       </c>
@@ -3976,7 +4009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>167</v>
       </c>
@@ -4002,7 +4035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>167</v>
       </c>
@@ -4028,7 +4061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>167</v>
       </c>
@@ -4054,7 +4087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>167</v>
       </c>
@@ -4080,7 +4113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>167</v>
       </c>
@@ -4106,7 +4139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>167</v>
       </c>
@@ -4132,7 +4165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>167</v>
       </c>
@@ -4158,7 +4191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>167</v>
       </c>
@@ -4184,7 +4217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>167</v>
       </c>
@@ -4210,7 +4243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>167</v>
       </c>
@@ -4236,7 +4269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>167</v>
       </c>
@@ -4262,7 +4295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>167</v>
       </c>
@@ -4288,7 +4321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>167</v>
       </c>
@@ -4314,7 +4347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>167</v>
       </c>
@@ -4340,7 +4373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>167</v>
       </c>
@@ -4366,7 +4399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>167</v>
       </c>
@@ -4392,7 +4425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>193</v>
       </c>
@@ -4415,7 +4448,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>193</v>
       </c>
@@ -4441,7 +4474,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>193</v>
       </c>
@@ -4467,7 +4500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>193</v>
       </c>
@@ -4493,7 +4526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>193</v>
       </c>
@@ -4519,7 +4552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>193</v>
       </c>
@@ -4545,7 +4578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>193</v>
       </c>
@@ -4571,7 +4604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>193</v>
       </c>
@@ -4597,7 +4630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>193</v>
       </c>
@@ -4623,7 +4656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>193</v>
       </c>
@@ -4649,7 +4682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>193</v>
       </c>
@@ -4675,7 +4708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>193</v>
       </c>
@@ -4701,7 +4734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>193</v>
       </c>
@@ -4727,7 +4760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>193</v>
       </c>
@@ -4753,7 +4786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>193</v>
       </c>
@@ -4779,7 +4812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>193</v>
       </c>
@@ -4805,7 +4838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>193</v>
       </c>
@@ -4831,7 +4864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>193</v>
       </c>
@@ -4857,7 +4890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>193</v>
       </c>
@@ -4883,7 +4916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>193</v>
       </c>
@@ -4909,7 +4942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>193</v>
       </c>
@@ -4935,7 +4968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>198</v>
       </c>
@@ -4955,6 +4988,107 @@
         <v>9</v>
       </c>
       <c r="H149" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>201</v>
+      </c>
+      <c r="C150" t="s">
+        <v>202</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" t="s">
+        <v>201</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>203</v>
+      </c>
+      <c r="C151" t="s">
+        <v>204</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F151" t="s">
+        <v>205</v>
+      </c>
+      <c r="G151" t="s">
+        <v>201</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>206</v>
+      </c>
+      <c r="C152" t="s">
+        <v>207</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F152" t="s">
+        <v>208</v>
+      </c>
+      <c r="G152" t="s">
+        <v>203</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>209</v>
+      </c>
+      <c r="C153" t="s">
+        <v>210</v>
+      </c>
+      <c r="D153">
+        <v>3</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153" t="s">
+        <v>211</v>
+      </c>
+      <c r="G153" t="s">
+        <v>203</v>
+      </c>
+      <c r="H153" s="2" t="s">
         <v>12</v>
       </c>
     </row>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250D9C4A-C9E4-4B3F-B323-ED8BFA22252B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169A2F75-0D04-4EDA-9D8F-E1A33C8A3637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="6800" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23370" yWindow="6980" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -63,15 +74,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
     <t>UTO</t>
   </si>
   <si>
@@ -103,6 +105,15 @@
   </si>
   <si>
     <t>UTO/CEN/FOR/CAP</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Postal code</t>
   </si>
 </sst>
 </file>
@@ -558,10 +569,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -570,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -581,22 +592,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
@@ -607,22 +618,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
+      <c r="E4" t="s">
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
@@ -633,22 +644,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>10</v>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169A2F75-0D04-4EDA-9D8F-E1A33C8A3637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFE0ACD-0BB1-482E-882C-24B7875BCE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23370" yWindow="6980" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="5770" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>lang_code</t>
   </si>
@@ -80,40 +80,58 @@
     <t>Utopia</t>
   </si>
   <si>
-    <t>CEN</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>UTO/CEN</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>Forest</t>
-  </si>
-  <si>
-    <t>UTO/CEN/FOR</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>Captial</t>
-  </si>
-  <si>
-    <t>UTO/CEN/FOR/CAP</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
     <t>City</t>
   </si>
   <si>
-    <t>Postal code</t>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>ZON</t>
+  </si>
+  <si>
+    <t>ZONE</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>PROVINCE</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>UTO/REG</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN/ZON</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN/250</t>
   </si>
 </sst>
 </file>
@@ -528,13 +546,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.81640625" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" customWidth="1"/>
     <col min="5" max="5" width="23.453125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" customWidth="1"/>
     <col min="8" max="8" width="8.453125" style="2"/>
   </cols>
   <sheetData>
@@ -577,7 +596,7 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
@@ -592,19 +611,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -618,22 +637,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
@@ -644,7 +663,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -653,15 +672,67 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
         <v>21</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>250</v>
+      </c>
+      <c r="C7">
+        <v>2500</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFE0ACD-0BB1-482E-882C-24B7875BCE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB24DAD-44D3-468B-A4A6-5AA437005798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="5770" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4420" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>lang_code</t>
   </si>
@@ -80,33 +80,12 @@
     <t>Utopia</t>
   </si>
   <si>
-    <t>City</t>
-  </si>
-  <si>
     <t>Region</t>
   </si>
   <si>
     <t>Province</t>
   </si>
   <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>ZON</t>
-  </si>
-  <si>
-    <t>ZONE</t>
-  </si>
-  <si>
-    <t>Canberra</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
     <t>REGION</t>
   </si>
   <si>
@@ -119,19 +98,19 @@
     <t>REG</t>
   </si>
   <si>
-    <t>UTO/REG</t>
-  </si>
-  <si>
-    <t>UTO/REG/PRO</t>
-  </si>
-  <si>
-    <t>UTO/REG/PRO/CAN</t>
-  </si>
-  <si>
-    <t>UTO/REG/PRO/CAN/ZON</t>
-  </si>
-  <si>
-    <t>UTO/REG/PRO/CAN/250</t>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>UTO/ALL</t>
+  </si>
+  <si>
+    <t>UTO/ALL/REG</t>
+  </si>
+  <si>
+    <t>UTO/REG/REG/PRO</t>
   </si>
 </sst>
 </file>
@@ -546,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.81640625" customWidth="1"/>
@@ -611,19 +590,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -637,22 +616,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
@@ -663,78 +642,35 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="E6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>250</v>
-      </c>
-      <c r="C7">
-        <v>2500</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -2,35 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB24DAD-44D3-468B-A4A6-5AA437005798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291DE009-7C1D-4171-9665-A69AC25D7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15680" yWindow="4420" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="3590" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="86">
   <si>
     <t>lang_code</t>
   </si>
@@ -68,49 +54,235 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
     <t>TRUE</t>
   </si>
   <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>Pays</t>
+  </si>
+  <si>
+    <t>NTH</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>RSK</t>
+  </si>
+  <si>
+    <t>RabatSaleKenitra</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Rabat-Salé-Kénitra</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>RBT</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>KTA</t>
+  </si>
+  <si>
+    <t>Kenitra</t>
+  </si>
+  <si>
+    <t>Kénitra</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>Salé </t>
+  </si>
+  <si>
+    <t>Sala</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>Casablanca-Settat</t>
+  </si>
+  <si>
+    <t>BSN</t>
+  </si>
+  <si>
+    <t>Benslimane</t>
+  </si>
+  <si>
+    <t>CSB</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Settat</t>
+  </si>
+  <si>
+    <t>ORT</t>
+  </si>
+  <si>
+    <t>Oriental</t>
+  </si>
+  <si>
+    <t>NDR</t>
+  </si>
+  <si>
+    <t>Nador</t>
+  </si>
+  <si>
+    <t>BRK</t>
+  </si>
+  <si>
+    <t>Berkane</t>
+  </si>
+  <si>
+    <t>JRD</t>
+  </si>
+  <si>
+    <t>Jerada </t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Sud</t>
+  </si>
+  <si>
+    <t>MRS</t>
+  </si>
+  <si>
+    <t>Marrakesh-Safi</t>
+  </si>
+  <si>
+    <t>SAF</t>
+  </si>
+  <si>
+    <t>Safi </t>
+  </si>
+  <si>
+    <t>YSF</t>
+  </si>
+  <si>
+    <t>Youssoufia </t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>Souss-Massa</t>
+  </si>
+  <si>
+    <t>Sus-Massa</t>
+  </si>
+  <si>
+    <t>TTA</t>
+  </si>
+  <si>
+    <t>Tata </t>
+  </si>
+  <si>
+    <t>TZT</t>
+  </si>
+  <si>
+    <t>Tiznit</t>
+  </si>
+  <si>
     <t>UTO</t>
   </si>
   <si>
     <t>Utopia</t>
   </si>
   <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>REGION</t>
-  </si>
-  <si>
-    <t>PROVINCE</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>REG</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>UTO/ALL</t>
-  </si>
-  <si>
-    <t>UTO/ALL/REG</t>
-  </si>
-  <si>
-    <t>UTO/REG/REG/PRO</t>
+    <t>UTO/NTH</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/RBT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/KTA</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/SAL</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/BSN</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/CSB</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/STT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/NDR</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/BRK</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/JRD</t>
+  </si>
+  <si>
+    <t>UTO/STH</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS/SAF</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS/YSF</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS/TTA</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS/TZT</t>
   </si>
 </sst>
 </file>
@@ -140,7 +312,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -163,49 +335,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -229,9 +366,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -239,39 +376,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -323,7 +460,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -375,7 +512,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,13 +571,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -449,6 +579,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -513,11 +650,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,40 +682,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.7265625" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="2"/>
+    <col min="8" max="8" width="8.453125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -567,48 +719,45 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -616,64 +765,1042 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="G5" t="s">
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E6"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E8"/>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291DE009-7C1D-4171-9665-A69AC25D7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="3590" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$64</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
   <si>
     <t>lang_code</t>
   </si>
@@ -57,6 +60,9 @@
     <t>MOR</t>
   </si>
   <si>
+    <t>MyCountry</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
     <t>fra</t>
   </si>
   <si>
+    <t>Maroc</t>
+  </si>
+  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -78,6 +87,9 @@
     <t>Direction</t>
   </si>
   <si>
+    <t>MOR/NTH</t>
+  </si>
+  <si>
     <t>Nord</t>
   </si>
   <si>
@@ -90,6 +102,9 @@
     <t>Region</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK</t>
+  </si>
+  <si>
     <t>Rabat-Salé-Kénitra</t>
   </si>
   <si>
@@ -105,12 +120,18 @@
     <t>Province</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/RBT</t>
+  </si>
+  <si>
     <t>KTA</t>
   </si>
   <si>
     <t>Kenitra</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/KTA</t>
+  </si>
+  <si>
     <t>Kénitra</t>
   </si>
   <si>
@@ -120,6 +141,9 @@
     <t>Salé </t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/SAL</t>
+  </si>
+  <si>
     <t>Sala</t>
   </si>
   <si>
@@ -129,54 +153,81 @@
     <t>Casablanca-Settat</t>
   </si>
   <si>
+    <t>MOR/NTH/CST</t>
+  </si>
+  <si>
     <t>BSN</t>
   </si>
   <si>
     <t>Benslimane</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/BSN</t>
+  </si>
+  <si>
     <t>CSB</t>
   </si>
   <si>
     <t>Casablanca</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/CSB</t>
+  </si>
+  <si>
     <t>STT</t>
   </si>
   <si>
     <t>Settat</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/STT</t>
+  </si>
+  <si>
     <t>ORT</t>
   </si>
   <si>
     <t>Oriental</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT</t>
+  </si>
+  <si>
     <t>NDR</t>
   </si>
   <si>
     <t>Nador</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/NDR</t>
+  </si>
+  <si>
     <t>BRK</t>
   </si>
   <si>
     <t>Berkane</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/BRK</t>
+  </si>
+  <si>
     <t>JRD</t>
   </si>
   <si>
     <t>Jerada </t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/JRD</t>
+  </si>
+  <si>
     <t>STH</t>
   </si>
   <si>
     <t>South</t>
   </si>
   <si>
+    <t>MOR/STH</t>
+  </si>
+  <si>
     <t>Sud</t>
   </si>
   <si>
@@ -186,24 +237,36 @@
     <t>Marrakesh-Safi</t>
   </si>
   <si>
+    <t>MOR/STH/MRS</t>
+  </si>
+  <si>
     <t>SAF</t>
   </si>
   <si>
     <t>Safi </t>
   </si>
   <si>
+    <t>MOR/STH/MRS/SAF</t>
+  </si>
+  <si>
     <t>YSF</t>
   </si>
   <si>
     <t>Youssoufia </t>
   </si>
   <si>
+    <t>MOR/STH/MRS/YSF</t>
+  </si>
+  <si>
     <t>SOS</t>
   </si>
   <si>
     <t>Souss-Massa</t>
   </si>
   <si>
+    <t>MOR/STH/SOS</t>
+  </si>
+  <si>
     <t>Sus-Massa</t>
   </si>
   <si>
@@ -213,83 +276,368 @@
     <t>Tata </t>
   </si>
   <si>
+    <t>MOR/STH/SOS/TTA</t>
+  </si>
+  <si>
     <t>TZT</t>
   </si>
   <si>
     <t>Tiznit</t>
   </si>
   <si>
-    <t>UTO</t>
-  </si>
-  <si>
-    <t>Utopia</t>
-  </si>
-  <si>
-    <t>UTO/NTH</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/RBT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/KTA</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/SAL</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/BSN</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/CSB</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/STT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/NDR</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/BRK</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/JRD</t>
-  </si>
-  <si>
-    <t>UTO/STH</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS/SAF</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS/YSF</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS/TTA</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS/TZT</t>
+    <t>MOR/STH/SOS/TZT</t>
+  </si>
+  <si>
+    <t>ara</t>
+  </si>
+  <si>
+    <t>مايكونتري</t>
+  </si>
+  <si>
+    <t>دولة</t>
+  </si>
+  <si>
+    <t>شمال</t>
+  </si>
+  <si>
+    <t>اتجاه</t>
+  </si>
+  <si>
+    <t>الرباط ساليالقنيطرة</t>
+  </si>
+  <si>
+    <t>منطقة</t>
+  </si>
+  <si>
+    <t>الرباط</t>
+  </si>
+  <si>
+    <t>مقاطعة</t>
+  </si>
+  <si>
+    <t>القنيطرة</t>
+  </si>
+  <si>
+    <t>قذر</t>
+  </si>
+  <si>
+    <t>الدار البيضاء سطات</t>
+  </si>
+  <si>
+    <t>بن سليمان</t>
+  </si>
+  <si>
+    <t>الدار البيضاء</t>
+  </si>
+  <si>
+    <t>سطات</t>
+  </si>
+  <si>
+    <t>شرقية</t>
+  </si>
+  <si>
+    <t>الناظور</t>
+  </si>
+  <si>
+    <t>بركان</t>
+  </si>
+  <si>
+    <t>جرادة</t>
+  </si>
+  <si>
+    <t>جنوب</t>
+  </si>
+  <si>
+    <t>مراكشصف</t>
+  </si>
+  <si>
+    <t>صافي</t>
+  </si>
+  <si>
+    <t>اليوسفية</t>
+  </si>
+  <si>
+    <t>سوس ماسة</t>
+  </si>
+  <si>
+    <t>تاتا</t>
+  </si>
+  <si>
+    <t>تزنيت</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>ನನ್ನ ದೇಶ</t>
+  </si>
+  <si>
+    <t>ದೇಶ</t>
+  </si>
+  <si>
+    <t>ಉತ್ತರ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ನಿರ್ದೇಶನ</t>
+  </si>
+  <si>
+    <t>ರಬತ್ಸಾಲೆಕೆನಿತ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಪ್ರದೇಶ</t>
+  </si>
+  <si>
+    <t>ರಬತ್</t>
+  </si>
+  <si>
+    <t>ಪ್ರಾಂತ್ಯ</t>
+  </si>
+  <si>
+    <t>ಕೆನಿತ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಸಾಲೆ</t>
+  </si>
+  <si>
+    <t>ಕಾಸಾಬ್ಲಾಂಕಾ-ಸೆಟ್ಟಾಟ್</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ಪ್ರದೇಶ</t>
+  </si>
+  <si>
+    <t>ಬೆನ್ಸ್ಲಿಮನೆ</t>
+  </si>
+  <si>
+    <t>ಕಾಸಾಬ್ಲಾಂಕಾ</t>
+  </si>
+  <si>
+    <t>ಸೆಟ್ಟಾಟ್</t>
+  </si>
+  <si>
+    <t>ಓರಿಯೆಂಟಲ್</t>
+  </si>
+  <si>
+    <t>ನಾಡೋರ್</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ಪ್ರಾಂತ್ಯ</t>
+  </si>
+  <si>
+    <t>ಬರ್ಕಾನೆ</t>
+  </si>
+  <si>
+    <t>ಜೆರಾಡಾ</t>
+  </si>
+  <si>
+    <t>ದಕ್ಷಿಣ</t>
+  </si>
+  <si>
+    <t>ಮರಕೇಶ್-ಸಫಿ</t>
+  </si>
+  <si>
+    <t>ಸಫಿ</t>
+  </si>
+  <si>
+    <t>ಯೂಸುಫಿಯಾ</t>
+  </si>
+  <si>
+    <t>ಸೌಸ್-ಮಸ್ಸಾ</t>
+  </si>
+  <si>
+    <t>ಟಾಟಾ</t>
+  </si>
+  <si>
+    <t>ಟಿಜ್ನಿಟ್</t>
+  </si>
+  <si>
+    <t>hin</t>
+  </si>
+  <si>
+    <t>मेरा देश</t>
+  </si>
+  <si>
+    <t>देश</t>
+  </si>
+  <si>
+    <t>उत्तर</t>
+  </si>
+  <si>
+    <t>दिशा</t>
+  </si>
+  <si>
+    <t>रबातबिक्रीकेनित्रा</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> क्षेत्र</t>
+  </si>
+  <si>
+    <t>रबात</t>
+  </si>
+  <si>
+    <t>प्रांत</t>
+  </si>
+  <si>
+    <t>केनिट्रा</t>
+  </si>
+  <si>
+    <t>बिक्री</t>
+  </si>
+  <si>
+    <t>कैसाब्लांका-सेटाटा</t>
+  </si>
+  <si>
+    <t>बेंस्लीमेन</t>
+  </si>
+  <si>
+    <t>कैसाब्लांका</t>
+  </si>
+  <si>
+    <t>सेत्तैत</t>
+  </si>
+  <si>
+    <t>ओरिएंटल</t>
+  </si>
+  <si>
+    <t>नादोरो</t>
+  </si>
+  <si>
+    <t>बेर्कने</t>
+  </si>
+  <si>
+    <t>जेराडा</t>
+  </si>
+  <si>
+    <t>दक्षिण</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> दिशा</t>
+  </si>
+  <si>
+    <t>मराकेश-सफी</t>
+  </si>
+  <si>
+    <t>साफी</t>
+  </si>
+  <si>
+    <t>युसूफिया </t>
+  </si>
+  <si>
+    <t>सूस-मस्सा</t>
+  </si>
+  <si>
+    <t>टाटा</t>
+  </si>
+  <si>
+    <t>टिज़निट</t>
+  </si>
+  <si>
+    <t>tam</t>
+  </si>
+  <si>
+    <t>என் நாடு</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> நாடு</t>
+  </si>
+  <si>
+    <t>வடக்கு</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> திசையில்</t>
+  </si>
+  <si>
+    <t>ரபத்சலேகெனிட்ரா</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> பிராந்தியம்</t>
+  </si>
+  <si>
+    <t>ரபாத்</t>
+  </si>
+  <si>
+    <t>மாகாணம்</t>
+  </si>
+  <si>
+    <t>கெனிட்ரா</t>
+  </si>
+  <si>
+    <t>சேலே</t>
+  </si>
+  <si>
+    <t>காசாபிளாங்கா-செட்டாட்</t>
+  </si>
+  <si>
+    <t>பென்ஸ்லிமேன்</t>
+  </si>
+  <si>
+    <t>காசாபிளாங்கா</t>
+  </si>
+  <si>
+    <t>செட்டாட்</t>
+  </si>
+  <si>
+    <t>ஓரியண்டல்</t>
+  </si>
+  <si>
+    <t>நாடோர்</t>
+  </si>
+  <si>
+    <t>பெர்கேன்</t>
+  </si>
+  <si>
+    <t>ஜெராடா</t>
+  </si>
+  <si>
+    <t>தெற்கு</t>
+  </si>
+  <si>
+    <t>மராகேஷ்-சஃபி</t>
+  </si>
+  <si>
+    <t>சாஃபி</t>
+  </si>
+  <si>
+    <t>யூசுஃபியா</t>
+  </si>
+  <si>
+    <t>சௌஸ்-மாசா</t>
+  </si>
+  <si>
+    <t>டாடா</t>
+  </si>
+  <si>
+    <t>டிஸ்னிட்</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>khm</t>
+  </si>
+  <si>
+    <t>ប្រទេសខ្ញុំ</t>
+  </si>
+  <si>
+    <t>ប្រទេស</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -303,6 +651,18 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -312,7 +672,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -335,17 +695,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -366,9 +802,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -376,39 +812,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -460,7 +896,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -512,7 +948,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -571,6 +1007,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -579,13 +1022,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -650,31 +1086,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -682,1125 +1098,3868 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H149"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="8.453125" style="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>22</v>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
-      <c r="E10" t="s">
-        <v>25</v>
+      <c r="E10" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" t="s">
-        <v>20</v>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
-        <v>22</v>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>25</v>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
-      <c r="E17" t="s">
-        <v>25</v>
+      <c r="E17" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" t="s">
-        <v>25</v>
+      <c r="E18" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" t="s">
-        <v>25</v>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" t="s">
         <v>39</v>
       </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
         <v>39</v>
       </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H21" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
-      <c r="E22" t="s">
-        <v>20</v>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
-      <c r="E23" t="s">
-        <v>22</v>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="E24" t="s">
-        <v>25</v>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="E25" t="s">
-        <v>25</v>
+      <c r="E25" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="E26" t="s">
-        <v>25</v>
+      <c r="E26" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="E27" t="s">
-        <v>25</v>
+      <c r="E27" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
-        <v>25</v>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="E29" t="s">
-        <v>25</v>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
-      <c r="E30" t="s">
-        <v>16</v>
+      <c r="E30" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31" t="s">
-        <v>16</v>
+      <c r="E31" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
-      <c r="E32" t="s">
-        <v>20</v>
+      <c r="E32" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33" t="s">
-        <v>22</v>
+      <c r="E33" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="E34" t="s">
-        <v>25</v>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="E35" t="s">
-        <v>25</v>
+      <c r="E35" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" t="s">
-        <v>25</v>
+      <c r="E36" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="E37" t="s">
-        <v>25</v>
+      <c r="E37" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
-      <c r="E38" t="s">
-        <v>20</v>
+      <c r="E38" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
-      <c r="E39" t="s">
-        <v>22</v>
+      <c r="E39" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40" t="s">
-        <v>25</v>
+      <c r="E40" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="E41" t="s">
-        <v>25</v>
+      <c r="E41" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="E42" t="s">
-        <v>25</v>
+      <c r="E42" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F42" t="s">
         <v>85</v>
       </c>
       <c r="G42" t="s">
-        <v>57</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" t="s">
-        <v>25</v>
+      <c r="E43" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="F43" t="s">
         <v>85</v>
       </c>
       <c r="G43" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
         <v>57</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>11</v>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" t="s">
+        <v>51</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" t="s">
+        <v>51</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>92</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" t="s">
+        <v>63</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>67</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" t="s">
+        <v>75</v>
+      </c>
+      <c r="G61" t="s">
+        <v>67</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s">
+        <v>63</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F66" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F70" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F73" t="s">
+        <v>47</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" t="s">
+        <v>127</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F74" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" t="s">
+        <v>128</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" t="s">
+        <v>53</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" t="s">
+        <v>54</v>
+      </c>
+      <c r="C76" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F76" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76" t="s">
+        <v>51</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F77" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" t="s">
+        <v>51</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F78" t="s">
+        <v>62</v>
+      </c>
+      <c r="G78" t="s">
+        <v>51</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79" t="s">
+        <v>133</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" t="s">
+        <v>65</v>
+      </c>
+      <c r="G79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>112</v>
+      </c>
+      <c r="B80" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F80" t="s">
+        <v>69</v>
+      </c>
+      <c r="G80" t="s">
+        <v>63</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>75</v>
+      </c>
+      <c r="G82" t="s">
+        <v>67</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>112</v>
+      </c>
+      <c r="B83" t="s">
+        <v>76</v>
+      </c>
+      <c r="C83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F83" t="s">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s">
+        <v>63</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>112</v>
+      </c>
+      <c r="B84" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" t="s">
+        <v>138</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F84" t="s">
+        <v>82</v>
+      </c>
+      <c r="G84" t="s">
+        <v>76</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" t="s">
+        <v>76</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>140</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>141</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F87" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>140</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>140</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F91" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>140</v>
+      </c>
+      <c r="B92" t="s">
+        <v>39</v>
+      </c>
+      <c r="C92" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" t="s">
+        <v>39</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>140</v>
+      </c>
+      <c r="B94" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F94" t="s">
+        <v>47</v>
+      </c>
+      <c r="G94" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>140</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F95" t="s">
+        <v>50</v>
+      </c>
+      <c r="G95" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>140</v>
+      </c>
+      <c r="B96" t="s">
+        <v>51</v>
+      </c>
+      <c r="C96" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G96" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>140</v>
+      </c>
+      <c r="B97" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F97" t="s">
+        <v>56</v>
+      </c>
+      <c r="G97" t="s">
+        <v>51</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>140</v>
+      </c>
+      <c r="B98" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F98" t="s">
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>51</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99">
+        <v>3</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" t="s">
+        <v>51</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100" t="s">
+        <v>63</v>
+      </c>
+      <c r="C100" t="s">
+        <v>159</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F100" t="s">
+        <v>65</v>
+      </c>
+      <c r="G100" t="s">
+        <v>9</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>161</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F101" t="s">
+        <v>69</v>
+      </c>
+      <c r="G101" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>140</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" t="s">
+        <v>72</v>
+      </c>
+      <c r="G102" t="s">
+        <v>67</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>140</v>
+      </c>
+      <c r="B103" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s">
+        <v>67</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>140</v>
+      </c>
+      <c r="B104" t="s">
+        <v>76</v>
+      </c>
+      <c r="C104" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F104" t="s">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s">
+        <v>63</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" t="s">
+        <v>80</v>
+      </c>
+      <c r="C105" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105">
+        <v>3</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F105" t="s">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s">
+        <v>76</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" t="s">
+        <v>166</v>
+      </c>
+      <c r="D106">
+        <v>3</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F106" t="s">
+        <v>85</v>
+      </c>
+      <c r="G106" t="s">
+        <v>76</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>168</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F107" t="s">
+        <v>9</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>170</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F108" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" t="s">
+        <v>9</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" t="s">
+        <v>172</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F109" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>167</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F110" t="s">
+        <v>30</v>
+      </c>
+      <c r="G110" t="s">
+        <v>21</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>167</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" t="s">
+        <v>176</v>
+      </c>
+      <c r="D111">
+        <v>3</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>177</v>
+      </c>
+      <c r="D112">
+        <v>3</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>167</v>
+      </c>
+      <c r="B113" t="s">
+        <v>39</v>
+      </c>
+      <c r="C113" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>167</v>
+      </c>
+      <c r="B114" t="s">
+        <v>42</v>
+      </c>
+      <c r="C114" t="s">
+        <v>179</v>
+      </c>
+      <c r="D114">
+        <v>3</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F114" t="s">
+        <v>44</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>167</v>
+      </c>
+      <c r="B115" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115">
+        <v>3</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F115" t="s">
+        <v>47</v>
+      </c>
+      <c r="G115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>167</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" t="s">
+        <v>181</v>
+      </c>
+      <c r="D116">
+        <v>3</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F116" t="s">
+        <v>50</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>167</v>
+      </c>
+      <c r="B117" t="s">
+        <v>51</v>
+      </c>
+      <c r="C117" t="s">
+        <v>182</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F117" t="s">
+        <v>53</v>
+      </c>
+      <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>167</v>
+      </c>
+      <c r="B118" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" t="s">
+        <v>183</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F118" t="s">
+        <v>56</v>
+      </c>
+      <c r="G118" t="s">
+        <v>51</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>167</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" t="s">
+        <v>184</v>
+      </c>
+      <c r="D119">
+        <v>3</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F119" t="s">
+        <v>59</v>
+      </c>
+      <c r="G119" t="s">
+        <v>51</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>167</v>
+      </c>
+      <c r="B120" t="s">
+        <v>60</v>
+      </c>
+      <c r="C120" t="s">
+        <v>185</v>
+      </c>
+      <c r="D120">
+        <v>3</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F120" t="s">
+        <v>62</v>
+      </c>
+      <c r="G120" t="s">
+        <v>51</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>167</v>
+      </c>
+      <c r="B121" t="s">
+        <v>63</v>
+      </c>
+      <c r="C121" t="s">
+        <v>186</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F121" t="s">
+        <v>65</v>
+      </c>
+      <c r="G121" t="s">
+        <v>9</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>167</v>
+      </c>
+      <c r="B122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F122" t="s">
+        <v>69</v>
+      </c>
+      <c r="G122" t="s">
+        <v>63</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" t="s">
+        <v>70</v>
+      </c>
+      <c r="C123" t="s">
+        <v>188</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F123" t="s">
+        <v>72</v>
+      </c>
+      <c r="G123" t="s">
+        <v>67</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>167</v>
+      </c>
+      <c r="B124" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" t="s">
+        <v>189</v>
+      </c>
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F124" t="s">
+        <v>75</v>
+      </c>
+      <c r="G124" t="s">
+        <v>67</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>167</v>
+      </c>
+      <c r="B125" t="s">
+        <v>76</v>
+      </c>
+      <c r="C125" t="s">
+        <v>190</v>
+      </c>
+      <c r="D125">
+        <v>2</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F125" t="s">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s">
+        <v>63</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>167</v>
+      </c>
+      <c r="B126" t="s">
+        <v>80</v>
+      </c>
+      <c r="C126" t="s">
+        <v>191</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F126" t="s">
+        <v>82</v>
+      </c>
+      <c r="G126" t="s">
+        <v>76</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
+        <v>83</v>
+      </c>
+      <c r="C127" t="s">
+        <v>192</v>
+      </c>
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F127" t="s">
+        <v>85</v>
+      </c>
+      <c r="G127" t="s">
+        <v>76</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>193</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>194</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>194</v>
+      </c>
+      <c r="F128" t="s">
+        <v>9</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>193</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129" t="s">
+        <v>195</v>
+      </c>
+      <c r="F129" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>193</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>196</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+      <c r="E130" t="s">
+        <v>196</v>
+      </c>
+      <c r="F130" t="s">
+        <v>24</v>
+      </c>
+      <c r="G130" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>193</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" t="s">
+        <v>197</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+      <c r="E131" t="s">
+        <v>197</v>
+      </c>
+      <c r="F131" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>193</v>
+      </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" t="s">
+        <v>197</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+      <c r="E132" t="s">
+        <v>197</v>
+      </c>
+      <c r="F132" t="s">
+        <v>33</v>
+      </c>
+      <c r="G132" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>193</v>
+      </c>
+      <c r="B133" t="s">
+        <v>35</v>
+      </c>
+      <c r="C133" t="s">
+        <v>197</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="E133" t="s">
+        <v>197</v>
+      </c>
+      <c r="F133" t="s">
+        <v>37</v>
+      </c>
+      <c r="G133" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>193</v>
+      </c>
+      <c r="B134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C134" t="s">
+        <v>196</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>196</v>
+      </c>
+      <c r="F134" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>193</v>
+      </c>
+      <c r="B135" t="s">
+        <v>42</v>
+      </c>
+      <c r="C135" t="s">
+        <v>197</v>
+      </c>
+      <c r="D135">
+        <v>3</v>
+      </c>
+      <c r="E135" t="s">
+        <v>197</v>
+      </c>
+      <c r="F135" t="s">
+        <v>44</v>
+      </c>
+      <c r="G135" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>193</v>
+      </c>
+      <c r="B136" t="s">
+        <v>45</v>
+      </c>
+      <c r="C136" t="s">
+        <v>197</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="E136" t="s">
+        <v>197</v>
+      </c>
+      <c r="F136" t="s">
+        <v>47</v>
+      </c>
+      <c r="G136" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>193</v>
+      </c>
+      <c r="B137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137" t="s">
+        <v>197</v>
+      </c>
+      <c r="D137">
+        <v>3</v>
+      </c>
+      <c r="E137" t="s">
+        <v>197</v>
+      </c>
+      <c r="F137" t="s">
+        <v>50</v>
+      </c>
+      <c r="G137" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>193</v>
+      </c>
+      <c r="B138" t="s">
+        <v>51</v>
+      </c>
+      <c r="C138" t="s">
+        <v>196</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" t="s">
+        <v>196</v>
+      </c>
+      <c r="F138" t="s">
+        <v>53</v>
+      </c>
+      <c r="G138" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>193</v>
+      </c>
+      <c r="B139" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" t="s">
+        <v>197</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139" t="s">
+        <v>197</v>
+      </c>
+      <c r="F139" t="s">
+        <v>56</v>
+      </c>
+      <c r="G139" t="s">
+        <v>51</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>193</v>
+      </c>
+      <c r="B140" t="s">
+        <v>57</v>
+      </c>
+      <c r="C140" t="s">
+        <v>197</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="E140" t="s">
+        <v>197</v>
+      </c>
+      <c r="F140" t="s">
+        <v>59</v>
+      </c>
+      <c r="G140" t="s">
+        <v>51</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>193</v>
+      </c>
+      <c r="B141" t="s">
+        <v>60</v>
+      </c>
+      <c r="C141" t="s">
+        <v>197</v>
+      </c>
+      <c r="D141">
+        <v>3</v>
+      </c>
+      <c r="E141" t="s">
+        <v>197</v>
+      </c>
+      <c r="F141" t="s">
+        <v>62</v>
+      </c>
+      <c r="G141" t="s">
+        <v>51</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>193</v>
+      </c>
+      <c r="B142" t="s">
+        <v>63</v>
+      </c>
+      <c r="C142" t="s">
+        <v>195</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
+        <v>195</v>
+      </c>
+      <c r="F142" t="s">
+        <v>65</v>
+      </c>
+      <c r="G142" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>193</v>
+      </c>
+      <c r="B143" t="s">
+        <v>67</v>
+      </c>
+      <c r="C143" t="s">
+        <v>196</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143" t="s">
+        <v>196</v>
+      </c>
+      <c r="F143" t="s">
+        <v>69</v>
+      </c>
+      <c r="G143" t="s">
+        <v>63</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>193</v>
+      </c>
+      <c r="B144" t="s">
+        <v>70</v>
+      </c>
+      <c r="C144" t="s">
+        <v>197</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+      <c r="E144" t="s">
+        <v>197</v>
+      </c>
+      <c r="F144" t="s">
+        <v>72</v>
+      </c>
+      <c r="G144" t="s">
+        <v>67</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>193</v>
+      </c>
+      <c r="B145" t="s">
+        <v>73</v>
+      </c>
+      <c r="C145" t="s">
+        <v>197</v>
+      </c>
+      <c r="D145">
+        <v>3</v>
+      </c>
+      <c r="E145" t="s">
+        <v>197</v>
+      </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>193</v>
+      </c>
+      <c r="B146" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" t="s">
+        <v>196</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146" t="s">
+        <v>196</v>
+      </c>
+      <c r="F146" t="s">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>193</v>
+      </c>
+      <c r="B147" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" t="s">
+        <v>197</v>
+      </c>
+      <c r="D147">
+        <v>3</v>
+      </c>
+      <c r="E147" t="s">
+        <v>197</v>
+      </c>
+      <c r="F147" t="s">
+        <v>82</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>193</v>
+      </c>
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
+        <v>197</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="E148" t="s">
+        <v>197</v>
+      </c>
+      <c r="F148" t="s">
+        <v>85</v>
+      </c>
+      <c r="G148" t="s">
+        <v>76</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>198</v>
+      </c>
+      <c r="B149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" t="s">
+        <v>199</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F149" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C5B98A-DB5F-4425-9190-9283C96A0248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4790" yWindow="4270" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$68</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="209">
   <si>
     <t>lang_code</t>
   </si>
@@ -631,6 +631,30 @@
   </si>
   <si>
     <t>ប្រទេស</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>Utopia</t>
+  </si>
+  <si>
+    <t>NORTH</t>
+  </si>
+  <si>
+    <t>UTO/NORTH</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>PROVINCE</t>
+  </si>
+  <si>
+    <t>UTO/NORTH/REGION</t>
+  </si>
+  <si>
+    <t>UTO/NORTH/REGION/PROVINCE</t>
   </si>
 </sst>
 </file>
@@ -649,7 +673,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1098,17 +1122,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H153"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="2"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1134,15 +1158,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1151,252 +1175,249 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>204</v>
+      </c>
+      <c r="G3" t="s">
+        <v>201</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1405,7 +1426,7 @@
         <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>21</v>
@@ -1414,15 +1435,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1431,7 +1452,7 @@
         <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
         <v>21</v>
@@ -1440,67 +1461,67 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1509,24 +1530,24 @@
         <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1535,76 +1556,76 @@
         <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -1613,7 +1634,7 @@
         <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G20" t="s">
         <v>39</v>
@@ -1622,15 +1643,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1639,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s">
         <v>39</v>
@@ -1648,67 +1669,67 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1717,24 +1738,24 @@
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1743,76 +1764,76 @@
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1821,7 +1842,7 @@
         <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
         <v>51</v>
@@ -1830,15 +1851,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1847,7 +1868,7 @@
         <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G29" t="s">
         <v>51</v>
@@ -1856,275 +1877,275 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2133,24 +2154,24 @@
         <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2159,229 +2180,229 @@
         <v>29</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>13</v>
       </c>
       <c r="B43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" t="s">
         <v>83</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C46" t="s">
         <v>84</v>
       </c>
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43" s="8" t="s">
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F46" t="s">
         <v>85</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G46" t="s">
         <v>76</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>90</v>
-      </c>
-      <c r="F45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46" t="s">
-        <v>92</v>
-      </c>
-      <c r="F46" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" t="s">
-        <v>16</v>
-      </c>
       <c r="H46" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47" t="s">
-        <v>94</v>
+      <c r="E47" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
-      </c>
-      <c r="G48" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2390,7 +2411,7 @@
         <v>92</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G50" t="s">
         <v>16</v>
@@ -2399,15 +2420,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2416,24 +2437,24 @@
         <v>94</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -2442,24 +2463,24 @@
         <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -2468,24 +2489,24 @@
         <v>94</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2494,7 +2515,7 @@
         <v>92</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G54" t="s">
         <v>16</v>
@@ -2503,15 +2524,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D55">
         <v>3</v>
@@ -2520,24 +2541,24 @@
         <v>94</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -2546,24 +2567,24 @@
         <v>94</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -2572,76 +2593,76 @@
         <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -2650,24 +2671,24 @@
         <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G60" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2676,76 +2697,76 @@
         <v>94</v>
       </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G61" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F63" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2754,186 +2775,186 @@
         <v>94</v>
       </c>
       <c r="F64" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" t="s">
+        <v>67</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" t="s">
+        <v>75</v>
+      </c>
+      <c r="G65" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F66" t="s">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" t="s">
+        <v>110</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s">
+        <v>76</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>94</v>
+      </c>
+      <c r="F68" t="s">
         <v>85</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G68" t="s">
         <v>76</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>112</v>
-      </c>
-      <c r="B65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" t="s">
-        <v>113</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F65" t="s">
-        <v>9</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="s">
-        <v>115</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F66" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" t="s">
-        <v>9</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" t="s">
-        <v>21</v>
-      </c>
-      <c r="C67" t="s">
-        <v>117</v>
-      </c>
-      <c r="D67">
-        <v>2</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F67" t="s">
-        <v>24</v>
-      </c>
-      <c r="G67" t="s">
-        <v>16</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" t="s">
-        <v>119</v>
-      </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F68" t="s">
-        <v>30</v>
-      </c>
-      <c r="G68" t="s">
-        <v>21</v>
-      </c>
       <c r="H68" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D69">
-        <v>3</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>120</v>
+        <v>0</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>33</v>
-      </c>
-      <c r="G69" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -2942,15 +2963,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -2959,24 +2980,24 @@
         <v>120</v>
       </c>
       <c r="F72" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -2985,24 +3006,24 @@
         <v>120</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>112</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -3011,24 +3032,24 @@
         <v>120</v>
       </c>
       <c r="F74" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G74" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>112</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -3037,7 +3058,7 @@
         <v>124</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
@@ -3046,145 +3067,145 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>112</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D76">
         <v>3</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F76" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G76" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D77">
         <v>3</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F77" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G77" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C78" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F78" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G79" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3193,24 +3214,24 @@
         <v>130</v>
       </c>
       <c r="F81" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -3219,255 +3240,255 @@
         <v>130</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G82" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G83" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F84" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G84" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>112</v>
       </c>
       <c r="B85" t="s">
+        <v>70</v>
+      </c>
+      <c r="C85" t="s">
+        <v>135</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F85" t="s">
+        <v>72</v>
+      </c>
+      <c r="G85" t="s">
+        <v>67</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" t="s">
+        <v>136</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F86" t="s">
+        <v>75</v>
+      </c>
+      <c r="G86" t="s">
+        <v>67</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" t="s">
+        <v>137</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F87" t="s">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s">
+        <v>63</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88" t="s">
+        <v>138</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F88" t="s">
+        <v>82</v>
+      </c>
+      <c r="G88" t="s">
+        <v>76</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" t="s">
         <v>83</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C89" t="s">
         <v>139</v>
       </c>
-      <c r="D85">
-        <v>3</v>
-      </c>
-      <c r="E85" s="10" t="s">
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F89" t="s">
         <v>85</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G89" t="s">
         <v>76</v>
       </c>
-      <c r="H85" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>140</v>
-      </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>141</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F86" t="s">
-        <v>9</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>140</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="s">
-        <v>143</v>
-      </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F87" t="s">
-        <v>19</v>
-      </c>
-      <c r="G87" t="s">
-        <v>9</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>140</v>
-      </c>
-      <c r="B88" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" t="s">
-        <v>145</v>
-      </c>
-      <c r="D88">
-        <v>2</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F88" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" t="s">
-        <v>16</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>140</v>
-      </c>
-      <c r="B89" t="s">
-        <v>27</v>
-      </c>
-      <c r="C89" t="s">
-        <v>147</v>
-      </c>
-      <c r="D89">
-        <v>3</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F89" t="s">
-        <v>30</v>
-      </c>
-      <c r="G89" t="s">
-        <v>21</v>
-      </c>
       <c r="H89" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>140</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="F90" t="s">
-        <v>33</v>
-      </c>
-      <c r="G90" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>140</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>140</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -3476,7 +3497,7 @@
         <v>146</v>
       </c>
       <c r="F92" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
@@ -3485,15 +3506,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>140</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -3502,24 +3523,24 @@
         <v>148</v>
       </c>
       <c r="F93" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G93" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>140</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -3528,24 +3549,24 @@
         <v>148</v>
       </c>
       <c r="F94" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G94" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>140</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -3554,24 +3575,24 @@
         <v>148</v>
       </c>
       <c r="F95" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G95" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>140</v>
       </c>
       <c r="B96" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C96" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -3580,7 +3601,7 @@
         <v>146</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G96" t="s">
         <v>16</v>
@@ -3589,15 +3610,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>140</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -3606,24 +3627,24 @@
         <v>148</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G97" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>140</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C98" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -3632,24 +3653,24 @@
         <v>148</v>
       </c>
       <c r="F98" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G98" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>140</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -3658,76 +3679,76 @@
         <v>148</v>
       </c>
       <c r="F99" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F100" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G100" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>140</v>
       </c>
       <c r="B101" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F101" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G101" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C102" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -3736,24 +3757,24 @@
         <v>148</v>
       </c>
       <c r="F102" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D103">
         <v>3</v>
@@ -3762,76 +3783,76 @@
         <v>148</v>
       </c>
       <c r="F103" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G103" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>140</v>
       </c>
       <c r="B104" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C104" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G104" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C105" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F105" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G105" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>140</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C106" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -3840,177 +3861,177 @@
         <v>148</v>
       </c>
       <c r="F106" t="s">
+        <v>72</v>
+      </c>
+      <c r="G106" t="s">
+        <v>67</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>140</v>
+      </c>
+      <c r="B107" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" t="s">
+        <v>163</v>
+      </c>
+      <c r="D107">
+        <v>3</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="G107" t="s">
+        <v>67</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>140</v>
+      </c>
+      <c r="B108" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F108" t="s">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s">
+        <v>63</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F109" t="s">
+        <v>82</v>
+      </c>
+      <c r="G109" t="s">
+        <v>76</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>140</v>
+      </c>
+      <c r="B110" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" t="s">
+        <v>166</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F110" t="s">
         <v>85</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G110" t="s">
         <v>76</v>
       </c>
-      <c r="H106" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>167</v>
-      </c>
-      <c r="B107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" t="s">
-        <v>168</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F107" t="s">
-        <v>9</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>167</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="s">
-        <v>170</v>
-      </c>
-      <c r="D108">
-        <v>1</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F108" t="s">
-        <v>19</v>
-      </c>
-      <c r="G108" t="s">
-        <v>9</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>167</v>
-      </c>
-      <c r="B109" t="s">
-        <v>21</v>
-      </c>
-      <c r="C109" t="s">
-        <v>172</v>
-      </c>
-      <c r="D109">
-        <v>2</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F109" t="s">
-        <v>24</v>
-      </c>
-      <c r="G109" t="s">
-        <v>16</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>167</v>
-      </c>
-      <c r="B110" t="s">
-        <v>27</v>
-      </c>
-      <c r="C110" t="s">
-        <v>174</v>
-      </c>
-      <c r="D110">
-        <v>3</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F110" t="s">
-        <v>30</v>
-      </c>
-      <c r="G110" t="s">
-        <v>21</v>
-      </c>
       <c r="H110" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>167</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D111">
-        <v>3</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>175</v>
+        <v>0</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
-      </c>
-      <c r="G111" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>167</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F112" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G112" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -4019,7 +4040,7 @@
         <v>173</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
@@ -4028,15 +4049,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -4045,24 +4066,24 @@
         <v>175</v>
       </c>
       <c r="F114" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G114" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C115" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -4071,24 +4092,24 @@
         <v>175</v>
       </c>
       <c r="F115" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G115" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>167</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C116" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -4097,24 +4118,24 @@
         <v>175</v>
       </c>
       <c r="F116" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G116" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>167</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C117" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -4123,7 +4144,7 @@
         <v>173</v>
       </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G117" t="s">
         <v>16</v>
@@ -4132,15 +4153,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>167</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C118" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -4149,24 +4170,24 @@
         <v>175</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G118" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>167</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C119" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D119">
         <v>3</v>
@@ -4175,24 +4196,24 @@
         <v>175</v>
       </c>
       <c r="F119" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G119" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>167</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -4201,76 +4222,76 @@
         <v>175</v>
       </c>
       <c r="F120" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G120" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>167</v>
       </c>
       <c r="B121" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C121" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F121" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G121" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>167</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C122" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F122" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G122" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>167</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C123" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4279,24 +4300,24 @@
         <v>175</v>
       </c>
       <c r="F123" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G123" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>167</v>
       </c>
       <c r="B124" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C124" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D124">
         <v>3</v>
@@ -4305,76 +4326,76 @@
         <v>175</v>
       </c>
       <c r="F124" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G124" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>167</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F125" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G125" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>167</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C126" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F126" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G126" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>167</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C127" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D127">
         <v>3</v>
@@ -4383,174 +4404,174 @@
         <v>175</v>
       </c>
       <c r="F127" t="s">
+        <v>72</v>
+      </c>
+      <c r="G127" t="s">
+        <v>67</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" t="s">
+        <v>73</v>
+      </c>
+      <c r="C128" t="s">
+        <v>189</v>
+      </c>
+      <c r="D128">
+        <v>3</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F128" t="s">
+        <v>75</v>
+      </c>
+      <c r="G128" t="s">
+        <v>67</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" t="s">
+        <v>76</v>
+      </c>
+      <c r="C129" t="s">
+        <v>190</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F129" t="s">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s">
+        <v>63</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130" t="s">
+        <v>80</v>
+      </c>
+      <c r="C130" t="s">
+        <v>191</v>
+      </c>
+      <c r="D130">
+        <v>3</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F130" t="s">
+        <v>82</v>
+      </c>
+      <c r="G130" t="s">
+        <v>76</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" t="s">
+        <v>83</v>
+      </c>
+      <c r="C131" t="s">
+        <v>192</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F131" t="s">
         <v>85</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G131" t="s">
         <v>76</v>
       </c>
-      <c r="H127" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>193</v>
-      </c>
-      <c r="B128" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" t="s">
-        <v>194</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
-        <v>194</v>
-      </c>
-      <c r="F128" t="s">
-        <v>9</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>193</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="s">
-        <v>195</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129" t="s">
-        <v>195</v>
-      </c>
-      <c r="F129" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" t="s">
-        <v>9</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>193</v>
-      </c>
-      <c r="B130" t="s">
-        <v>21</v>
-      </c>
-      <c r="C130" t="s">
-        <v>196</v>
-      </c>
-      <c r="D130">
-        <v>2</v>
-      </c>
-      <c r="E130" t="s">
-        <v>196</v>
-      </c>
-      <c r="F130" t="s">
-        <v>24</v>
-      </c>
-      <c r="G130" t="s">
-        <v>16</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>193</v>
-      </c>
-      <c r="B131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C131" t="s">
-        <v>197</v>
-      </c>
-      <c r="D131">
-        <v>3</v>
-      </c>
-      <c r="E131" t="s">
-        <v>197</v>
-      </c>
-      <c r="F131" t="s">
-        <v>30</v>
-      </c>
-      <c r="G131" t="s">
-        <v>21</v>
-      </c>
       <c r="H131" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>193</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F132" t="s">
-        <v>33</v>
-      </c>
-      <c r="G132" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>193</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G133" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>193</v>
       </c>
       <c r="B134" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C134" t="s">
         <v>196</v>
@@ -4562,7 +4583,7 @@
         <v>196</v>
       </c>
       <c r="F134" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G134" t="s">
         <v>16</v>
@@ -4571,12 +4592,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>193</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C135" t="s">
         <v>197</v>
@@ -4588,21 +4609,21 @@
         <v>197</v>
       </c>
       <c r="F135" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G135" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>193</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
         <v>197</v>
@@ -4614,21 +4635,21 @@
         <v>197</v>
       </c>
       <c r="F136" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G136" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>193</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C137" t="s">
         <v>197</v>
@@ -4640,21 +4661,21 @@
         <v>197</v>
       </c>
       <c r="F137" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G137" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>193</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C138" t="s">
         <v>196</v>
@@ -4666,7 +4687,7 @@
         <v>196</v>
       </c>
       <c r="F138" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G138" t="s">
         <v>16</v>
@@ -4675,12 +4696,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>193</v>
       </c>
       <c r="B139" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C139" t="s">
         <v>197</v>
@@ -4692,21 +4713,21 @@
         <v>197</v>
       </c>
       <c r="F139" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G139" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>193</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C140" t="s">
         <v>197</v>
@@ -4718,21 +4739,21 @@
         <v>197</v>
       </c>
       <c r="F140" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G140" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>193</v>
       </c>
       <c r="B141" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C141" t="s">
         <v>197</v>
@@ -4744,73 +4765,73 @@
         <v>197</v>
       </c>
       <c r="F141" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G141" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>193</v>
       </c>
       <c r="B142" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C142" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F142" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G142" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>193</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C143" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E143" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F143" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G143" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>193</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C144" t="s">
         <v>197</v>
@@ -4822,21 +4843,21 @@
         <v>197</v>
       </c>
       <c r="F144" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G144" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>193</v>
       </c>
       <c r="B145" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C145" t="s">
         <v>197</v>
@@ -4848,73 +4869,73 @@
         <v>197</v>
       </c>
       <c r="F145" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G145" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>193</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C146" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F146" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G146" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>193</v>
       </c>
       <c r="B147" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C147" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F147" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G147" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>193</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C148" t="s">
         <v>197</v>
@@ -4926,40 +4947,144 @@
         <v>197</v>
       </c>
       <c r="F148" t="s">
+        <v>72</v>
+      </c>
+      <c r="G148" t="s">
+        <v>67</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>193</v>
+      </c>
+      <c r="B149" t="s">
+        <v>73</v>
+      </c>
+      <c r="C149" t="s">
+        <v>197</v>
+      </c>
+      <c r="D149">
+        <v>3</v>
+      </c>
+      <c r="E149" t="s">
+        <v>197</v>
+      </c>
+      <c r="F149" t="s">
+        <v>75</v>
+      </c>
+      <c r="G149" t="s">
+        <v>67</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>193</v>
+      </c>
+      <c r="B150" t="s">
+        <v>76</v>
+      </c>
+      <c r="C150" t="s">
+        <v>196</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150" t="s">
+        <v>196</v>
+      </c>
+      <c r="F150" t="s">
+        <v>78</v>
+      </c>
+      <c r="G150" t="s">
+        <v>63</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>193</v>
+      </c>
+      <c r="B151" t="s">
+        <v>80</v>
+      </c>
+      <c r="C151" t="s">
+        <v>197</v>
+      </c>
+      <c r="D151">
+        <v>3</v>
+      </c>
+      <c r="E151" t="s">
+        <v>197</v>
+      </c>
+      <c r="F151" t="s">
+        <v>82</v>
+      </c>
+      <c r="G151" t="s">
+        <v>76</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>193</v>
+      </c>
+      <c r="B152" t="s">
+        <v>83</v>
+      </c>
+      <c r="C152" t="s">
+        <v>197</v>
+      </c>
+      <c r="D152">
+        <v>3</v>
+      </c>
+      <c r="E152" t="s">
+        <v>197</v>
+      </c>
+      <c r="F152" t="s">
         <v>85</v>
       </c>
-      <c r="G148" t="s">
+      <c r="G152" t="s">
         <v>76</v>
       </c>
-      <c r="H148" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="H152" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
         <v>198</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B153" t="s">
         <v>9</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C153" t="s">
         <v>199</v>
       </c>
-      <c r="D149">
+      <c r="D153">
         <v>0</v>
       </c>
-      <c r="E149" s="11" t="s">
+      <c r="E153" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F149" t="s">
+      <c r="F153" t="s">
         <v>9</v>
       </c>
-      <c r="H149" s="2" t="s">
+      <c r="H153" s="2" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A68" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79109238-4D04-402F-B87F-5EF179621EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA502CC-63B5-4FC1-871A-EA3248175FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-130" yWindow="-130" windowWidth="38660" windowHeight="21140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$8</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="85">
   <si>
     <t>lang_code</t>
   </si>
@@ -57,73 +54,232 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
     <t>TRUE</t>
   </si>
   <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>Pays</t>
+  </si>
+  <si>
+    <t>NTH</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
     <t>Direction</t>
   </si>
   <si>
+    <t>MOR/NTH</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>RSK</t>
+  </si>
+  <si>
+    <t>RabatSaleKenitra</t>
+  </si>
+  <si>
     <t>Region</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK</t>
+  </si>
+  <si>
+    <t>Rabat-Salé-Kénitra</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>RBT</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
     <t>Province</t>
   </si>
   <si>
-    <t>UTO</t>
+    <t>MOR/NTH/RSK/RBT</t>
+  </si>
+  <si>
+    <t>KTA</t>
+  </si>
+  <si>
+    <t>Kenitra</t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK/KTA</t>
+  </si>
+  <si>
+    <t>Kénitra</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>Salé </t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK/SAL</t>
+  </si>
+  <si>
+    <t>Sala</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>Casablanca-Settat</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST</t>
+  </si>
+  <si>
+    <t>BSN</t>
+  </si>
+  <si>
+    <t>Benslimane</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/BSN</t>
+  </si>
+  <si>
+    <t>CSB</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/CSB</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Settat</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/STT</t>
+  </si>
+  <si>
+    <t>ORT</t>
+  </si>
+  <si>
+    <t>Oriental</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT</t>
+  </si>
+  <si>
+    <t>NDR</t>
+  </si>
+  <si>
+    <t>Nador</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/NDR</t>
+  </si>
+  <si>
+    <t>BRK</t>
+  </si>
+  <si>
+    <t>Berkane</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/BRK</t>
+  </si>
+  <si>
+    <t>JRD</t>
+  </si>
+  <si>
+    <t>Jerada </t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/JRD</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>MOR/STH</t>
+  </si>
+  <si>
+    <t>Sud</t>
+  </si>
+  <si>
+    <t>MRS</t>
+  </si>
+  <si>
+    <t>Marrakesh-Safi</t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS</t>
+  </si>
+  <si>
+    <t>SAF</t>
+  </si>
+  <si>
+    <t>Safi </t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS/SAF</t>
+  </si>
+  <si>
+    <t>YSF</t>
+  </si>
+  <si>
+    <t>Youssoufia </t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS/YSF</t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>Souss-Massa</t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS</t>
+  </si>
+  <si>
+    <t>Sus-Massa</t>
+  </si>
+  <si>
+    <t>TTA</t>
+  </si>
+  <si>
+    <t>Tata </t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS/TTA</t>
+  </si>
+  <si>
+    <t>TZT</t>
+  </si>
+  <si>
+    <t>Tiznit</t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS/TZT</t>
   </si>
   <si>
     <t>Utopia</t>
-  </si>
-  <si>
-    <t>NORTH</t>
-  </si>
-  <si>
-    <t>UTO/NORTH</t>
-  </si>
-  <si>
-    <t>PROVINCE1</t>
-  </si>
-  <si>
-    <t>REGION1</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>PRO1</t>
-  </si>
-  <si>
-    <t>UTO/NORTH/REGION1</t>
-  </si>
-  <si>
-    <t>UTO/NORTH/REGION1/PROVINCE1</t>
-  </si>
-  <si>
-    <t>SOUTH</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>PRO2</t>
-  </si>
-  <si>
-    <t>PROVINCE2</t>
-  </si>
-  <si>
-    <t>REGION2</t>
-  </si>
-  <si>
-    <t>UTO/SOUTH/REGION2</t>
-  </si>
-  <si>
-    <t>UTO/SOUTH/REGION2/PROVINCE2</t>
-  </si>
-  <si>
-    <t>UTO/SOUTH</t>
   </si>
 </sst>
 </file>
@@ -142,7 +298,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,7 +309,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -176,68 +332,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -258,9 +363,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,39 +373,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -352,7 +457,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -404,7 +509,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,13 +568,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -478,6 +576,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -542,11 +647,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,224 +679,1125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="2"/>
+    <col min="8" max="8" width="8.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
+      <c r="E7" t="s">
+        <v>24</v>
       </c>
       <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="G7" t="s">
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>10</v>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s">
+        <v>74</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
+        <v>74</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA502CC-63B5-4FC1-871A-EA3248175FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$64</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
   <si>
     <t>lang_code</t>
   </si>
@@ -57,6 +60,9 @@
     <t>MOR</t>
   </si>
   <si>
+    <t>MyCountry</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
     <t>fra</t>
   </si>
   <si>
+    <t>Maroc</t>
+  </si>
+  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -279,14 +288,356 @@
     <t>MOR/STH/SOS/TZT</t>
   </si>
   <si>
-    <t>Utopia</t>
+    <t>ara</t>
+  </si>
+  <si>
+    <t>مايكونتري</t>
+  </si>
+  <si>
+    <t>دولة</t>
+  </si>
+  <si>
+    <t>شمال</t>
+  </si>
+  <si>
+    <t>اتجاه</t>
+  </si>
+  <si>
+    <t>الرباط ساليالقنيطرة</t>
+  </si>
+  <si>
+    <t>منطقة</t>
+  </si>
+  <si>
+    <t>الرباط</t>
+  </si>
+  <si>
+    <t>مقاطعة</t>
+  </si>
+  <si>
+    <t>القنيطرة</t>
+  </si>
+  <si>
+    <t>قذر</t>
+  </si>
+  <si>
+    <t>الدار البيضاء سطات</t>
+  </si>
+  <si>
+    <t>بن سليمان</t>
+  </si>
+  <si>
+    <t>الدار البيضاء</t>
+  </si>
+  <si>
+    <t>سطات</t>
+  </si>
+  <si>
+    <t>شرقية</t>
+  </si>
+  <si>
+    <t>الناظور</t>
+  </si>
+  <si>
+    <t>بركان</t>
+  </si>
+  <si>
+    <t>جرادة</t>
+  </si>
+  <si>
+    <t>جنوب</t>
+  </si>
+  <si>
+    <t>مراكشصف</t>
+  </si>
+  <si>
+    <t>صافي</t>
+  </si>
+  <si>
+    <t>اليوسفية</t>
+  </si>
+  <si>
+    <t>سوس ماسة</t>
+  </si>
+  <si>
+    <t>تاتا</t>
+  </si>
+  <si>
+    <t>تزنيت</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>ನನ್ನ ದೇಶ</t>
+  </si>
+  <si>
+    <t>ದೇಶ</t>
+  </si>
+  <si>
+    <t>ಉತ್ತರ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ನಿರ್ದೇಶನ</t>
+  </si>
+  <si>
+    <t>ರಬತ್ಸಾಲೆಕೆನಿತ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಪ್ರದೇಶ</t>
+  </si>
+  <si>
+    <t>ರಬತ್</t>
+  </si>
+  <si>
+    <t>ಪ್ರಾಂತ್ಯ</t>
+  </si>
+  <si>
+    <t>ಕೆನಿತ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಸಾಲೆ</t>
+  </si>
+  <si>
+    <t>ಕಾಸಾಬ್ಲಾಂಕಾ-ಸೆಟ್ಟಾಟ್</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ಪ್ರದೇಶ</t>
+  </si>
+  <si>
+    <t>ಬೆನ್ಸ್ಲಿಮನೆ</t>
+  </si>
+  <si>
+    <t>ಕಾಸಾಬ್ಲಾಂಕಾ</t>
+  </si>
+  <si>
+    <t>ಸೆಟ್ಟಾಟ್</t>
+  </si>
+  <si>
+    <t>ಓರಿಯೆಂಟಲ್</t>
+  </si>
+  <si>
+    <t>ನಾಡೋರ್</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ಪ್ರಾಂತ್ಯ</t>
+  </si>
+  <si>
+    <t>ಬರ್ಕಾನೆ</t>
+  </si>
+  <si>
+    <t>ಜೆರಾಡಾ</t>
+  </si>
+  <si>
+    <t>ದಕ್ಷಿಣ</t>
+  </si>
+  <si>
+    <t>ಮರಕೇಶ್-ಸಫಿ</t>
+  </si>
+  <si>
+    <t>ಸಫಿ</t>
+  </si>
+  <si>
+    <t>ಯೂಸುಫಿಯಾ</t>
+  </si>
+  <si>
+    <t>ಸೌಸ್-ಮಸ್ಸಾ</t>
+  </si>
+  <si>
+    <t>ಟಾಟಾ</t>
+  </si>
+  <si>
+    <t>ಟಿಜ್ನಿಟ್</t>
+  </si>
+  <si>
+    <t>hin</t>
+  </si>
+  <si>
+    <t>मेरा देश</t>
+  </si>
+  <si>
+    <t>देश</t>
+  </si>
+  <si>
+    <t>उत्तर</t>
+  </si>
+  <si>
+    <t>दिशा</t>
+  </si>
+  <si>
+    <t>रबातबिक्रीकेनित्रा</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> क्षेत्र</t>
+  </si>
+  <si>
+    <t>रबात</t>
+  </si>
+  <si>
+    <t>प्रांत</t>
+  </si>
+  <si>
+    <t>केनिट्रा</t>
+  </si>
+  <si>
+    <t>बिक्री</t>
+  </si>
+  <si>
+    <t>कैसाब्लांका-सेटाटा</t>
+  </si>
+  <si>
+    <t>बेंस्लीमेन</t>
+  </si>
+  <si>
+    <t>कैसाब्लांका</t>
+  </si>
+  <si>
+    <t>सेत्तैत</t>
+  </si>
+  <si>
+    <t>ओरिएंटल</t>
+  </si>
+  <si>
+    <t>नादोरो</t>
+  </si>
+  <si>
+    <t>बेर्कने</t>
+  </si>
+  <si>
+    <t>जेराडा</t>
+  </si>
+  <si>
+    <t>दक्षिण</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> दिशा</t>
+  </si>
+  <si>
+    <t>मराकेश-सफी</t>
+  </si>
+  <si>
+    <t>साफी</t>
+  </si>
+  <si>
+    <t>युसूफिया </t>
+  </si>
+  <si>
+    <t>सूस-मस्सा</t>
+  </si>
+  <si>
+    <t>टाटा</t>
+  </si>
+  <si>
+    <t>टिज़निट</t>
+  </si>
+  <si>
+    <t>tam</t>
+  </si>
+  <si>
+    <t>என் நாடு</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> நாடு</t>
+  </si>
+  <si>
+    <t>வடக்கு</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> திசையில்</t>
+  </si>
+  <si>
+    <t>ரபத்சலேகெனிட்ரா</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> பிராந்தியம்</t>
+  </si>
+  <si>
+    <t>ரபாத்</t>
+  </si>
+  <si>
+    <t>மாகாணம்</t>
+  </si>
+  <si>
+    <t>கெனிட்ரா</t>
+  </si>
+  <si>
+    <t>சேலே</t>
+  </si>
+  <si>
+    <t>காசாபிளாங்கா-செட்டாட்</t>
+  </si>
+  <si>
+    <t>பென்ஸ்லிமேன்</t>
+  </si>
+  <si>
+    <t>காசாபிளாங்கா</t>
+  </si>
+  <si>
+    <t>செட்டாட்</t>
+  </si>
+  <si>
+    <t>ஓரியண்டல்</t>
+  </si>
+  <si>
+    <t>நாடோர்</t>
+  </si>
+  <si>
+    <t>பெர்கேன்</t>
+  </si>
+  <si>
+    <t>ஜெராடா</t>
+  </si>
+  <si>
+    <t>தெற்கு</t>
+  </si>
+  <si>
+    <t>மராகேஷ்-சஃபி</t>
+  </si>
+  <si>
+    <t>சாஃபி</t>
+  </si>
+  <si>
+    <t>யூசுஃபியா</t>
+  </si>
+  <si>
+    <t>சௌஸ்-மாசா</t>
+  </si>
+  <si>
+    <t>டாடா</t>
+  </si>
+  <si>
+    <t>டிஸ்னிட்</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>khm</t>
+  </si>
+  <si>
+    <t>ប្រទេសខ្ញុំ</t>
+  </si>
+  <si>
+    <t>ប្រទេស</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -300,6 +651,18 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -309,7 +672,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -332,17 +695,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -363,9 +802,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -373,39 +812,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -457,7 +896,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -509,7 +948,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -568,6 +1007,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -576,13 +1022,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -647,31 +1086,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -679,35 +1098,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="8.42578125" style="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
@@ -719,42 +1142,42 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -762,51 +1185,51 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -814,51 +1237,51 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
       <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -866,51 +1289,51 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
-        <v>27</v>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
-        <v>27</v>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -918,51 +1341,51 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -970,51 +1393,51 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="s">
-        <v>27</v>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
-        <v>27</v>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1022,51 +1445,51 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" t="s">
-        <v>21</v>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
-        <v>24</v>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1074,51 +1497,51 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>27</v>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
-      <c r="E17" t="s">
-        <v>27</v>
+      <c r="E17" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1126,51 +1549,51 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" t="s">
-        <v>27</v>
+      <c r="E18" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" t="s">
-        <v>27</v>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1178,51 +1601,51 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
-        <v>27</v>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
-      <c r="E21" t="s">
-        <v>27</v>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1230,51 +1653,51 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
-      <c r="E22" t="s">
-        <v>21</v>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
-      <c r="E23" t="s">
-        <v>24</v>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1282,51 +1705,51 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="E24" t="s">
-        <v>27</v>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="E25" t="s">
-        <v>27</v>
+      <c r="E25" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,51 +1757,51 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="E26" t="s">
-        <v>27</v>
+      <c r="E26" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="E27" t="s">
-        <v>27</v>
+      <c r="E27" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1386,51 +1809,51 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
-        <v>27</v>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="E29" t="s">
-        <v>27</v>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1438,51 +1861,51 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
-      <c r="E30" t="s">
-        <v>16</v>
+      <c r="E30" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>11</v>
+      <c r="H30" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31" t="s">
-        <v>16</v>
+      <c r="E31" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>11</v>
+      <c r="H31" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1490,51 +1913,51 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
-      <c r="E32" t="s">
-        <v>21</v>
+      <c r="E32" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33" t="s">
-        <v>24</v>
+      <c r="E33" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1542,51 +1965,51 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="E34" t="s">
-        <v>27</v>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="E35" t="s">
-        <v>27</v>
+      <c r="E35" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1594,51 +2017,51 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" t="s">
-        <v>27</v>
+      <c r="E36" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="E37" t="s">
-        <v>27</v>
+      <c r="E37" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1646,51 +2069,51 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
-      <c r="E38" t="s">
-        <v>21</v>
+      <c r="E38" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
-      <c r="E39" t="s">
-        <v>24</v>
+      <c r="E39" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1698,51 +2121,51 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40" t="s">
-        <v>27</v>
+      <c r="E40" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="E41" t="s">
-        <v>27</v>
+      <c r="E41" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1750,54 +2173,2793 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="E42" t="s">
-        <v>27</v>
+      <c r="E42" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" t="s">
+        <v>51</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" t="s">
+        <v>51</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>92</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" t="s">
+        <v>63</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>67</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" t="s">
+        <v>75</v>
+      </c>
+      <c r="G61" t="s">
+        <v>67</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s">
+        <v>63</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" t="s">
         <v>82</v>
       </c>
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="G63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F66" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" t="s">
         <v>27</v>
       </c>
-      <c r="F43" t="s">
+      <c r="C68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F70" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F73" t="s">
+        <v>47</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" t="s">
+        <v>127</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F74" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" t="s">
+        <v>128</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" t="s">
+        <v>53</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" t="s">
+        <v>54</v>
+      </c>
+      <c r="C76" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F76" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76" t="s">
+        <v>51</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F77" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" t="s">
+        <v>51</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F78" t="s">
+        <v>62</v>
+      </c>
+      <c r="G78" t="s">
+        <v>51</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79" t="s">
+        <v>133</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" t="s">
+        <v>65</v>
+      </c>
+      <c r="G79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>112</v>
+      </c>
+      <c r="B80" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F80" t="s">
+        <v>69</v>
+      </c>
+      <c r="G80" t="s">
+        <v>63</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>75</v>
+      </c>
+      <c r="G82" t="s">
+        <v>67</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>112</v>
+      </c>
+      <c r="B83" t="s">
+        <v>76</v>
+      </c>
+      <c r="C83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F83" t="s">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s">
+        <v>63</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>112</v>
+      </c>
+      <c r="B84" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" t="s">
+        <v>138</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F84" t="s">
+        <v>82</v>
+      </c>
+      <c r="G84" t="s">
+        <v>76</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" t="s">
         <v>83</v>
       </c>
-      <c r="G43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>11</v>
+      <c r="C85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" t="s">
+        <v>76</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>140</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>141</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F87" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>140</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>140</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F91" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>140</v>
+      </c>
+      <c r="B92" t="s">
+        <v>39</v>
+      </c>
+      <c r="C92" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" t="s">
+        <v>39</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>140</v>
+      </c>
+      <c r="B94" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F94" t="s">
+        <v>47</v>
+      </c>
+      <c r="G94" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>140</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F95" t="s">
+        <v>50</v>
+      </c>
+      <c r="G95" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>140</v>
+      </c>
+      <c r="B96" t="s">
+        <v>51</v>
+      </c>
+      <c r="C96" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G96" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>140</v>
+      </c>
+      <c r="B97" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F97" t="s">
+        <v>56</v>
+      </c>
+      <c r="G97" t="s">
+        <v>51</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>140</v>
+      </c>
+      <c r="B98" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F98" t="s">
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>51</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99">
+        <v>3</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" t="s">
+        <v>51</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100" t="s">
+        <v>63</v>
+      </c>
+      <c r="C100" t="s">
+        <v>159</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F100" t="s">
+        <v>65</v>
+      </c>
+      <c r="G100" t="s">
+        <v>9</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>161</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F101" t="s">
+        <v>69</v>
+      </c>
+      <c r="G101" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>140</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" t="s">
+        <v>72</v>
+      </c>
+      <c r="G102" t="s">
+        <v>67</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>140</v>
+      </c>
+      <c r="B103" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s">
+        <v>67</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>140</v>
+      </c>
+      <c r="B104" t="s">
+        <v>76</v>
+      </c>
+      <c r="C104" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F104" t="s">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s">
+        <v>63</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" t="s">
+        <v>80</v>
+      </c>
+      <c r="C105" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105">
+        <v>3</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F105" t="s">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s">
+        <v>76</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" t="s">
+        <v>166</v>
+      </c>
+      <c r="D106">
+        <v>3</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F106" t="s">
+        <v>85</v>
+      </c>
+      <c r="G106" t="s">
+        <v>76</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>168</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F107" t="s">
+        <v>9</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>170</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F108" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" t="s">
+        <v>9</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" t="s">
+        <v>172</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F109" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>167</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F110" t="s">
+        <v>30</v>
+      </c>
+      <c r="G110" t="s">
+        <v>21</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>167</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" t="s">
+        <v>176</v>
+      </c>
+      <c r="D111">
+        <v>3</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>177</v>
+      </c>
+      <c r="D112">
+        <v>3</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>167</v>
+      </c>
+      <c r="B113" t="s">
+        <v>39</v>
+      </c>
+      <c r="C113" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>167</v>
+      </c>
+      <c r="B114" t="s">
+        <v>42</v>
+      </c>
+      <c r="C114" t="s">
+        <v>179</v>
+      </c>
+      <c r="D114">
+        <v>3</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F114" t="s">
+        <v>44</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>167</v>
+      </c>
+      <c r="B115" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115">
+        <v>3</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F115" t="s">
+        <v>47</v>
+      </c>
+      <c r="G115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>167</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" t="s">
+        <v>181</v>
+      </c>
+      <c r="D116">
+        <v>3</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F116" t="s">
+        <v>50</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>167</v>
+      </c>
+      <c r="B117" t="s">
+        <v>51</v>
+      </c>
+      <c r="C117" t="s">
+        <v>182</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F117" t="s">
+        <v>53</v>
+      </c>
+      <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>167</v>
+      </c>
+      <c r="B118" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" t="s">
+        <v>183</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F118" t="s">
+        <v>56</v>
+      </c>
+      <c r="G118" t="s">
+        <v>51</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>167</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" t="s">
+        <v>184</v>
+      </c>
+      <c r="D119">
+        <v>3</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F119" t="s">
+        <v>59</v>
+      </c>
+      <c r="G119" t="s">
+        <v>51</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>167</v>
+      </c>
+      <c r="B120" t="s">
+        <v>60</v>
+      </c>
+      <c r="C120" t="s">
+        <v>185</v>
+      </c>
+      <c r="D120">
+        <v>3</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F120" t="s">
+        <v>62</v>
+      </c>
+      <c r="G120" t="s">
+        <v>51</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>167</v>
+      </c>
+      <c r="B121" t="s">
+        <v>63</v>
+      </c>
+      <c r="C121" t="s">
+        <v>186</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F121" t="s">
+        <v>65</v>
+      </c>
+      <c r="G121" t="s">
+        <v>9</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>167</v>
+      </c>
+      <c r="B122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F122" t="s">
+        <v>69</v>
+      </c>
+      <c r="G122" t="s">
+        <v>63</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" t="s">
+        <v>70</v>
+      </c>
+      <c r="C123" t="s">
+        <v>188</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F123" t="s">
+        <v>72</v>
+      </c>
+      <c r="G123" t="s">
+        <v>67</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>167</v>
+      </c>
+      <c r="B124" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" t="s">
+        <v>189</v>
+      </c>
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F124" t="s">
+        <v>75</v>
+      </c>
+      <c r="G124" t="s">
+        <v>67</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>167</v>
+      </c>
+      <c r="B125" t="s">
+        <v>76</v>
+      </c>
+      <c r="C125" t="s">
+        <v>190</v>
+      </c>
+      <c r="D125">
+        <v>2</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F125" t="s">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s">
+        <v>63</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>167</v>
+      </c>
+      <c r="B126" t="s">
+        <v>80</v>
+      </c>
+      <c r="C126" t="s">
+        <v>191</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F126" t="s">
+        <v>82</v>
+      </c>
+      <c r="G126" t="s">
+        <v>76</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
+        <v>83</v>
+      </c>
+      <c r="C127" t="s">
+        <v>192</v>
+      </c>
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F127" t="s">
+        <v>85</v>
+      </c>
+      <c r="G127" t="s">
+        <v>76</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>193</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>194</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>194</v>
+      </c>
+      <c r="F128" t="s">
+        <v>9</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>193</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129" t="s">
+        <v>195</v>
+      </c>
+      <c r="F129" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>193</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>196</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+      <c r="E130" t="s">
+        <v>196</v>
+      </c>
+      <c r="F130" t="s">
+        <v>24</v>
+      </c>
+      <c r="G130" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>193</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" t="s">
+        <v>197</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+      <c r="E131" t="s">
+        <v>197</v>
+      </c>
+      <c r="F131" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>193</v>
+      </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" t="s">
+        <v>197</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+      <c r="E132" t="s">
+        <v>197</v>
+      </c>
+      <c r="F132" t="s">
+        <v>33</v>
+      </c>
+      <c r="G132" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>193</v>
+      </c>
+      <c r="B133" t="s">
+        <v>35</v>
+      </c>
+      <c r="C133" t="s">
+        <v>197</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="E133" t="s">
+        <v>197</v>
+      </c>
+      <c r="F133" t="s">
+        <v>37</v>
+      </c>
+      <c r="G133" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>193</v>
+      </c>
+      <c r="B134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C134" t="s">
+        <v>196</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>196</v>
+      </c>
+      <c r="F134" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>193</v>
+      </c>
+      <c r="B135" t="s">
+        <v>42</v>
+      </c>
+      <c r="C135" t="s">
+        <v>197</v>
+      </c>
+      <c r="D135">
+        <v>3</v>
+      </c>
+      <c r="E135" t="s">
+        <v>197</v>
+      </c>
+      <c r="F135" t="s">
+        <v>44</v>
+      </c>
+      <c r="G135" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>193</v>
+      </c>
+      <c r="B136" t="s">
+        <v>45</v>
+      </c>
+      <c r="C136" t="s">
+        <v>197</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="E136" t="s">
+        <v>197</v>
+      </c>
+      <c r="F136" t="s">
+        <v>47</v>
+      </c>
+      <c r="G136" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>193</v>
+      </c>
+      <c r="B137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137" t="s">
+        <v>197</v>
+      </c>
+      <c r="D137">
+        <v>3</v>
+      </c>
+      <c r="E137" t="s">
+        <v>197</v>
+      </c>
+      <c r="F137" t="s">
+        <v>50</v>
+      </c>
+      <c r="G137" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>193</v>
+      </c>
+      <c r="B138" t="s">
+        <v>51</v>
+      </c>
+      <c r="C138" t="s">
+        <v>196</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" t="s">
+        <v>196</v>
+      </c>
+      <c r="F138" t="s">
+        <v>53</v>
+      </c>
+      <c r="G138" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>193</v>
+      </c>
+      <c r="B139" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" t="s">
+        <v>197</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139" t="s">
+        <v>197</v>
+      </c>
+      <c r="F139" t="s">
+        <v>56</v>
+      </c>
+      <c r="G139" t="s">
+        <v>51</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>193</v>
+      </c>
+      <c r="B140" t="s">
+        <v>57</v>
+      </c>
+      <c r="C140" t="s">
+        <v>197</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="E140" t="s">
+        <v>197</v>
+      </c>
+      <c r="F140" t="s">
+        <v>59</v>
+      </c>
+      <c r="G140" t="s">
+        <v>51</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>193</v>
+      </c>
+      <c r="B141" t="s">
+        <v>60</v>
+      </c>
+      <c r="C141" t="s">
+        <v>197</v>
+      </c>
+      <c r="D141">
+        <v>3</v>
+      </c>
+      <c r="E141" t="s">
+        <v>197</v>
+      </c>
+      <c r="F141" t="s">
+        <v>62</v>
+      </c>
+      <c r="G141" t="s">
+        <v>51</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>193</v>
+      </c>
+      <c r="B142" t="s">
+        <v>63</v>
+      </c>
+      <c r="C142" t="s">
+        <v>195</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
+        <v>195</v>
+      </c>
+      <c r="F142" t="s">
+        <v>65</v>
+      </c>
+      <c r="G142" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>193</v>
+      </c>
+      <c r="B143" t="s">
+        <v>67</v>
+      </c>
+      <c r="C143" t="s">
+        <v>196</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143" t="s">
+        <v>196</v>
+      </c>
+      <c r="F143" t="s">
+        <v>69</v>
+      </c>
+      <c r="G143" t="s">
+        <v>63</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>193</v>
+      </c>
+      <c r="B144" t="s">
+        <v>70</v>
+      </c>
+      <c r="C144" t="s">
+        <v>197</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+      <c r="E144" t="s">
+        <v>197</v>
+      </c>
+      <c r="F144" t="s">
+        <v>72</v>
+      </c>
+      <c r="G144" t="s">
+        <v>67</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>193</v>
+      </c>
+      <c r="B145" t="s">
+        <v>73</v>
+      </c>
+      <c r="C145" t="s">
+        <v>197</v>
+      </c>
+      <c r="D145">
+        <v>3</v>
+      </c>
+      <c r="E145" t="s">
+        <v>197</v>
+      </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>193</v>
+      </c>
+      <c r="B146" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" t="s">
+        <v>196</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146" t="s">
+        <v>196</v>
+      </c>
+      <c r="F146" t="s">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>193</v>
+      </c>
+      <c r="B147" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" t="s">
+        <v>197</v>
+      </c>
+      <c r="D147">
+        <v>3</v>
+      </c>
+      <c r="E147" t="s">
+        <v>197</v>
+      </c>
+      <c r="F147" t="s">
+        <v>82</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>193</v>
+      </c>
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
+        <v>197</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="E148" t="s">
+        <v>197</v>
+      </c>
+      <c r="F148" t="s">
+        <v>85</v>
+      </c>
+      <c r="G148" t="s">
+        <v>76</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>198</v>
+      </c>
+      <c r="B149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" t="s">
+        <v>199</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F149" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E142F1B7-93F7-435D-B3A9-E5405B52AFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>MOR</t>
   </si>
   <si>
-    <t>MyCountry</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>fra</t>
   </si>
   <si>
-    <t>Maroc</t>
-  </si>
-  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
     <t>Direction</t>
   </si>
   <si>
-    <t>MOR/NTH</t>
-  </si>
-  <si>
     <t>Nord</t>
   </si>
   <si>
@@ -102,9 +93,6 @@
     <t>Region</t>
   </si>
   <si>
-    <t>MOR/NTH/RSK</t>
-  </si>
-  <si>
     <t>Rabat-Salé-Kénitra</t>
   </si>
   <si>
@@ -120,18 +108,12 @@
     <t>Province</t>
   </si>
   <si>
-    <t>MOR/NTH/RSK/RBT</t>
-  </si>
-  <si>
     <t>KTA</t>
   </si>
   <si>
     <t>Kenitra</t>
   </si>
   <si>
-    <t>MOR/NTH/RSK/KTA</t>
-  </si>
-  <si>
     <t>Kénitra</t>
   </si>
   <si>
@@ -141,9 +123,6 @@
     <t>Salé </t>
   </si>
   <si>
-    <t>MOR/NTH/RSK/SAL</t>
-  </si>
-  <si>
     <t>Sala</t>
   </si>
   <si>
@@ -153,81 +132,54 @@
     <t>Casablanca-Settat</t>
   </si>
   <si>
-    <t>MOR/NTH/CST</t>
-  </si>
-  <si>
     <t>BSN</t>
   </si>
   <si>
     <t>Benslimane</t>
   </si>
   <si>
-    <t>MOR/NTH/CST/BSN</t>
-  </si>
-  <si>
     <t>CSB</t>
   </si>
   <si>
     <t>Casablanca</t>
   </si>
   <si>
-    <t>MOR/NTH/CST/CSB</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
     <t>Settat</t>
   </si>
   <si>
-    <t>MOR/NTH/CST/STT</t>
-  </si>
-  <si>
     <t>ORT</t>
   </si>
   <si>
     <t>Oriental</t>
   </si>
   <si>
-    <t>MOR/NTH/ORT</t>
-  </si>
-  <si>
     <t>NDR</t>
   </si>
   <si>
     <t>Nador</t>
   </si>
   <si>
-    <t>MOR/NTH/ORT/NDR</t>
-  </si>
-  <si>
     <t>BRK</t>
   </si>
   <si>
     <t>Berkane</t>
   </si>
   <si>
-    <t>MOR/NTH/ORT/BRK</t>
-  </si>
-  <si>
     <t>JRD</t>
   </si>
   <si>
     <t>Jerada </t>
   </si>
   <si>
-    <t>MOR/NTH/ORT/JRD</t>
-  </si>
-  <si>
     <t>STH</t>
   </si>
   <si>
     <t>South</t>
   </si>
   <si>
-    <t>MOR/STH</t>
-  </si>
-  <si>
     <t>Sud</t>
   </si>
   <si>
@@ -237,36 +189,24 @@
     <t>Marrakesh-Safi</t>
   </si>
   <si>
-    <t>MOR/STH/MRS</t>
-  </si>
-  <si>
     <t>SAF</t>
   </si>
   <si>
     <t>Safi </t>
   </si>
   <si>
-    <t>MOR/STH/MRS/SAF</t>
-  </si>
-  <si>
     <t>YSF</t>
   </si>
   <si>
     <t>Youssoufia </t>
   </si>
   <si>
-    <t>MOR/STH/MRS/YSF</t>
-  </si>
-  <si>
     <t>SOS</t>
   </si>
   <si>
     <t>Souss-Massa</t>
   </si>
   <si>
-    <t>MOR/STH/SOS</t>
-  </si>
-  <si>
     <t>Sus-Massa</t>
   </si>
   <si>
@@ -276,18 +216,12 @@
     <t>Tata </t>
   </si>
   <si>
-    <t>MOR/STH/SOS/TTA</t>
-  </si>
-  <si>
     <t>TZT</t>
   </si>
   <si>
     <t>Tiznit</t>
   </si>
   <si>
-    <t>MOR/STH/SOS/TZT</t>
-  </si>
-  <si>
     <t>ara</t>
   </si>
   <si>
@@ -631,6 +565,72 @@
   </si>
   <si>
     <t>ប្រទេស</t>
+  </si>
+  <si>
+    <t>Utopia</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>UTO/NTH</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/RBT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/KTA</t>
+  </si>
+  <si>
+    <t>UTO/NTH/RSK/SAL</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/BSN</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/CSB</t>
+  </si>
+  <si>
+    <t>UTO/NTH/CST/STT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/NDR</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/BRK</t>
+  </si>
+  <si>
+    <t>UTO/NTH/ORT/JRD</t>
+  </si>
+  <si>
+    <t>UTO/STH</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS/SAF</t>
+  </si>
+  <si>
+    <t>UTO/STH/MRS/YSF</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS/TTA</t>
+  </si>
+  <si>
+    <t>UTO/STH/SOS/TZT</t>
   </si>
 </sst>
 </file>
@@ -1099,16 +1099,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="2"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="4" max="4" width="16.86328125" customWidth="1"/>
+    <col min="5" max="5" width="23.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.265625" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1134,3828 +1134,3828 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G30" t="s">
         <v>9</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H36" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H40" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>13</v>
-      </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H42" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>13</v>
-      </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F43" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G43" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G45" t="s">
         <v>9</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F52" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D55">
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G55" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D56">
         <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D57">
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G58" t="s">
         <v>9</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" t="s">
+        <v>196</v>
+      </c>
+      <c r="G60" t="s">
+        <v>51</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" t="s">
         <v>86</v>
       </c>
-      <c r="B60" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" t="s">
-        <v>107</v>
-      </c>
-      <c r="D60">
-        <v>3</v>
-      </c>
-      <c r="E60" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
         <v>72</v>
       </c>
-      <c r="G60" t="s">
-        <v>67</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61">
-        <v>3</v>
-      </c>
-      <c r="E61" t="s">
-        <v>94</v>
-      </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G61" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F62" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F63" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G66" t="s">
         <v>9</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F69" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F72" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G72" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G73" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D74">
         <v>3</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F74" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G74" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="D76">
         <v>3</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F76" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G76" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D77">
         <v>3</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F77" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G77" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F78" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G78" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G79" t="s">
         <v>9</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" t="s">
         <v>112</v>
-      </c>
-      <c r="B80" t="s">
-        <v>67</v>
-      </c>
-      <c r="C80" t="s">
-        <v>134</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D81">
         <v>3</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F81" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G82" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D83">
         <v>2</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G83" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D84">
         <v>3</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F84" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D85">
         <v>3</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F85" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G85" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G87" t="s">
         <v>9</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C89" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D89">
         <v>3</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D90">
         <v>3</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G90" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F92" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F93" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G93" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C94" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D94">
         <v>3</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G94" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D95">
         <v>3</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F95" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B96" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C96" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D97">
         <v>3</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G97" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C98" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D98">
         <v>3</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F98" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="D99">
         <v>3</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G99" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="F100" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G100" t="s">
         <v>9</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D101">
         <v>2</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F101" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G101" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" t="s">
+        <v>53</v>
+      </c>
+      <c r="C102" t="s">
         <v>140</v>
       </c>
-      <c r="B102" t="s">
-        <v>70</v>
-      </c>
-      <c r="C102" t="s">
-        <v>162</v>
-      </c>
       <c r="D102">
         <v>3</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F102" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="D103">
         <v>3</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F103" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G103" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C104" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G104" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C105" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D105">
         <v>3</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F105" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G105" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="D106">
         <v>3</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F106" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G106" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="F107" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C108" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G108" t="s">
         <v>9</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C109" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F109" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G109" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D110">
         <v>3</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F110" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G110" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D111">
         <v>3</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G111" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C112" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="D112">
         <v>3</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F112" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G112" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C113" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C114" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D114">
         <v>3</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F114" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G114" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D115">
         <v>3</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F115" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G115" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C116" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="D116">
         <v>3</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F116" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G116" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C117" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G117" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C118" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D118">
         <v>3</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G118" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C119" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D119">
         <v>3</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F119" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="G119" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D120">
         <v>3</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F120" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="G120" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B121" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C121" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="F121" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G121" t="s">
         <v>9</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F122" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="G122" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
+        <v>145</v>
+      </c>
+      <c r="B123" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" t="s">
+        <v>166</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F123" t="s">
+        <v>196</v>
+      </c>
+      <c r="G123" t="s">
+        <v>51</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" t="s">
         <v>167</v>
       </c>
-      <c r="B123" t="s">
-        <v>70</v>
-      </c>
-      <c r="C123" t="s">
-        <v>188</v>
-      </c>
-      <c r="D123">
-        <v>3</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F123" t="s">
-        <v>72</v>
-      </c>
-      <c r="G123" t="s">
-        <v>67</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>167</v>
-      </c>
-      <c r="B124" t="s">
-        <v>73</v>
-      </c>
-      <c r="C124" t="s">
-        <v>189</v>
-      </c>
       <c r="D124">
         <v>3</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F124" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="G124" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C125" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="D125">
         <v>2</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F125" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G125" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C126" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="D126">
         <v>3</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F126" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G126" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C127" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D127">
         <v>3</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F127" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G127" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="F128" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F129" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G129" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C130" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F130" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G130" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B131" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C131" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D131">
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F131" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="G131" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C132" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D132">
         <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F132" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G132" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D133">
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="G133" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B134" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C134" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D134">
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F134" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G134" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C135" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D135">
         <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F135" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="G135" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C136" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D136">
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F136" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G136" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C137" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D137">
         <v>3</v>
       </c>
       <c r="E137" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F137" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="G137" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C138" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D138">
         <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F138" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G138" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
+        <v>171</v>
+      </c>
+      <c r="B139" t="s">
+        <v>42</v>
+      </c>
+      <c r="C139" t="s">
+        <v>175</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139" t="s">
+        <v>175</v>
+      </c>
+      <c r="F139" t="s">
+        <v>191</v>
+      </c>
+      <c r="G139" t="s">
+        <v>40</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" t="s">
+        <v>44</v>
+      </c>
+      <c r="C140" t="s">
+        <v>175</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="E140" t="s">
+        <v>175</v>
+      </c>
+      <c r="F140" t="s">
+        <v>192</v>
+      </c>
+      <c r="G140" t="s">
+        <v>40</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>171</v>
+      </c>
+      <c r="B141" t="s">
+        <v>46</v>
+      </c>
+      <c r="C141" t="s">
+        <v>175</v>
+      </c>
+      <c r="D141">
+        <v>3</v>
+      </c>
+      <c r="E141" t="s">
+        <v>175</v>
+      </c>
+      <c r="F141" t="s">
         <v>193</v>
       </c>
-      <c r="B139" t="s">
-        <v>54</v>
-      </c>
-      <c r="C139" t="s">
-        <v>197</v>
-      </c>
-      <c r="D139">
-        <v>3</v>
-      </c>
-      <c r="E139" t="s">
-        <v>197</v>
-      </c>
-      <c r="F139" t="s">
-        <v>56</v>
-      </c>
-      <c r="G139" t="s">
-        <v>51</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>193</v>
-      </c>
-      <c r="B140" t="s">
-        <v>57</v>
-      </c>
-      <c r="C140" t="s">
-        <v>197</v>
-      </c>
-      <c r="D140">
-        <v>3</v>
-      </c>
-      <c r="E140" t="s">
-        <v>197</v>
-      </c>
-      <c r="F140" t="s">
-        <v>59</v>
-      </c>
-      <c r="G140" t="s">
-        <v>51</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>193</v>
-      </c>
-      <c r="B141" t="s">
-        <v>60</v>
-      </c>
-      <c r="C141" t="s">
-        <v>197</v>
-      </c>
-      <c r="D141">
-        <v>3</v>
-      </c>
-      <c r="E141" t="s">
-        <v>197</v>
-      </c>
-      <c r="F141" t="s">
-        <v>62</v>
-      </c>
       <c r="G141" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B142" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F142" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G142" t="s">
         <v>9</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C143" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
+        <v>174</v>
+      </c>
+      <c r="F143" t="s">
+        <v>195</v>
+      </c>
+      <c r="G143" t="s">
+        <v>48</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>171</v>
+      </c>
+      <c r="B144" t="s">
+        <v>53</v>
+      </c>
+      <c r="C144" t="s">
+        <v>175</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+      <c r="E144" t="s">
+        <v>175</v>
+      </c>
+      <c r="F144" t="s">
         <v>196</v>
       </c>
-      <c r="F143" t="s">
-        <v>69</v>
-      </c>
-      <c r="G143" t="s">
-        <v>63</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>193</v>
-      </c>
-      <c r="B144" t="s">
-        <v>70</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="G144" t="s">
+        <v>51</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>171</v>
+      </c>
+      <c r="B145" t="s">
+        <v>55</v>
+      </c>
+      <c r="C145" t="s">
+        <v>175</v>
+      </c>
+      <c r="D145">
+        <v>3</v>
+      </c>
+      <c r="E145" t="s">
+        <v>175</v>
+      </c>
+      <c r="F145" t="s">
         <v>197</v>
       </c>
-      <c r="D144">
-        <v>3</v>
-      </c>
-      <c r="E144" t="s">
-        <v>197</v>
-      </c>
-      <c r="F144" t="s">
-        <v>72</v>
-      </c>
-      <c r="G144" t="s">
-        <v>67</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>193</v>
-      </c>
-      <c r="B145" t="s">
-        <v>73</v>
-      </c>
-      <c r="C145" t="s">
-        <v>197</v>
-      </c>
-      <c r="D145">
-        <v>3</v>
-      </c>
-      <c r="E145" t="s">
-        <v>197</v>
-      </c>
-      <c r="F145" t="s">
-        <v>75</v>
-      </c>
       <c r="G145" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C146" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D146">
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F146" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="G146" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D147">
         <v>3</v>
       </c>
       <c r="E147" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F147" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="G147" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C148" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D148">
         <v>3</v>
       </c>
       <c r="E148" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F148" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="G148" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B149" t="s">
         <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F149" t="s">
         <v>9</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E142F1B7-93F7-435D-B3A9-E5405B52AFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB2AD4-A27E-4980-A239-F702C2F8CC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,7 +1200,7 @@
         <v>181</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -1226,7 +1226,7 @@
         <v>181</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -1876,7 +1876,7 @@
         <v>194</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>11</v>
@@ -1902,7 +1902,7 @@
         <v>194</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>11</v>
@@ -2225,7 +2225,7 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
         <v>65</v>
@@ -2263,7 +2263,7 @@
         <v>181</v>
       </c>
       <c r="G45" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>11</v>
@@ -2601,7 +2601,7 @@
         <v>194</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>11</v>
@@ -2768,7 +2768,7 @@
         <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C65" t="s">
         <v>91</v>
@@ -2806,7 +2806,7 @@
         <v>181</v>
       </c>
       <c r="G66" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>11</v>
@@ -3144,7 +3144,7 @@
         <v>194</v>
       </c>
       <c r="G79" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>11</v>
@@ -3311,7 +3311,7 @@
         <v>118</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C86" t="s">
         <v>119</v>
@@ -3349,7 +3349,7 @@
         <v>181</v>
       </c>
       <c r="G87" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>11</v>
@@ -3687,7 +3687,7 @@
         <v>194</v>
       </c>
       <c r="G100" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>11</v>
@@ -3854,7 +3854,7 @@
         <v>145</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C107" t="s">
         <v>146</v>
@@ -3892,7 +3892,7 @@
         <v>181</v>
       </c>
       <c r="G108" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>11</v>
@@ -4230,7 +4230,7 @@
         <v>194</v>
       </c>
       <c r="G121" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>11</v>
@@ -4397,7 +4397,7 @@
         <v>171</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C128" t="s">
         <v>172</v>
@@ -4435,7 +4435,7 @@
         <v>181</v>
       </c>
       <c r="G129" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>11</v>
@@ -4773,7 +4773,7 @@
         <v>194</v>
       </c>
       <c r="G142" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>11</v>
@@ -4940,7 +4940,7 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
         <v>177</v>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB2AD4-A27E-4980-A239-F702C2F8CC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C564372-52EE-4433-BBB5-6C975C28E06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>11</v>
@@ -1174,7 +1174,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C564372-52EE-4433-BBB5-6C975C28E06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07888178-D28B-4740-AB9E-A160790F907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="200">
   <si>
     <t>lang_code</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>eng</t>
-  </si>
-  <si>
-    <t>MOR</t>
   </si>
   <si>
     <t>Country</t>
@@ -1139,45 +1136,45 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
@@ -1185,51 +1182,51 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
@@ -1237,51 +1234,51 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
@@ -1289,51 +1286,51 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
@@ -1341,51 +1338,51 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
@@ -1393,51 +1390,51 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
@@ -1445,51 +1442,51 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
         <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
@@ -1497,51 +1494,51 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
@@ -1549,51 +1546,51 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
@@ -1601,51 +1598,51 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
         <v>38</v>
       </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
@@ -1653,51 +1650,51 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
         <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
         <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
@@ -1705,51 +1702,51 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
         <v>42</v>
       </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
         <v>42</v>
       </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
@@ -1757,51 +1754,51 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
         <v>44</v>
       </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
@@ -1809,51 +1806,51 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
         <v>46</v>
       </c>
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
         <v>46</v>
       </c>
-      <c r="C29" t="s">
-        <v>47</v>
-      </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
@@ -1861,51 +1858,51 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
         <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
@@ -1913,51 +1910,51 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
         <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
         <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
@@ -1965,51 +1962,51 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
         <v>53</v>
       </c>
-      <c r="C34" t="s">
-        <v>54</v>
-      </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
         <v>53</v>
       </c>
-      <c r="C35" t="s">
-        <v>54</v>
-      </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -2017,51 +2014,51 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
         <v>55</v>
       </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
         <v>55</v>
       </c>
-      <c r="C37" t="s">
-        <v>56</v>
-      </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
@@ -2069,51 +2066,51 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
         <v>57</v>
-      </c>
-      <c r="C38" t="s">
-        <v>58</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
@@ -2121,51 +2118,51 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
-        <v>61</v>
-      </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
         <v>60</v>
       </c>
-      <c r="C41" t="s">
-        <v>61</v>
-      </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
@@ -2173,2789 +2170,2789 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="C42" t="s">
-        <v>63</v>
-      </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
         <v>62</v>
       </c>
-      <c r="C43" t="s">
-        <v>63</v>
-      </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" t="s">
         <v>64</v>
-      </c>
-      <c r="B44" t="s">
-        <v>180</v>
-      </c>
-      <c r="C44" t="s">
-        <v>65</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
         <v>71</v>
       </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47" t="s">
-        <v>72</v>
-      </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F52" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D55">
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D56">
         <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D57">
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F60" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" t="s">
         <v>90</v>
-      </c>
-      <c r="B65" t="s">
-        <v>180</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G66" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F67" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="F68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D74">
         <v>3</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F75" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D76">
-        <v>3</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>108</v>
-      </c>
       <c r="F76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D77">
         <v>3</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C79" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F80" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D81">
         <v>3</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F81" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G81" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F82" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G82" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D83">
         <v>2</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G83" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D84">
         <v>3</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D85">
         <v>3</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" t="s">
         <v>118</v>
-      </c>
-      <c r="B86" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" t="s">
-        <v>119</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F86" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G87" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
+        <v>124</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D89">
-        <v>3</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="F89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D90">
         <v>3</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D94">
         <v>3</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D95">
         <v>3</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F96" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D97">
         <v>3</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D98">
         <v>3</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F98" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D99">
         <v>3</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D101">
         <v>2</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C102" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D102">
         <v>3</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G102" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D103">
         <v>3</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F104" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C105" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D105">
         <v>3</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G105" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D106">
         <v>3</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F106" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G106" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
+        <v>144</v>
+      </c>
+      <c r="B107" t="s">
+        <v>179</v>
+      </c>
+      <c r="C107" t="s">
         <v>145</v>
-      </c>
-      <c r="B107" t="s">
-        <v>180</v>
-      </c>
-      <c r="C107" t="s">
-        <v>146</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F107" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G108" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F109" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
+        <v>151</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D110">
-        <v>3</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>153</v>
-      </c>
       <c r="F110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B111" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D111">
         <v>3</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F111" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C112" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D112">
         <v>3</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F113" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C114" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D114">
         <v>3</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F114" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D115">
         <v>3</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F115" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D116">
         <v>3</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F116" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C117" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F117" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C118" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D118">
         <v>3</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F118" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G118" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B119" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D119">
         <v>3</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F119" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B120" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C120" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D120">
         <v>3</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F120" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C121" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G121" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F122" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B123" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C123" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D123">
         <v>3</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G123" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D124">
         <v>3</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F124" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G124" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C125" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D125">
         <v>2</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F125" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G125" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B126" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C126" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D126">
         <v>3</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F126" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G126" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C127" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D127">
         <v>3</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F127" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G127" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
+        <v>170</v>
+      </c>
+      <c r="B128" t="s">
+        <v>179</v>
+      </c>
+      <c r="C128" t="s">
         <v>171</v>
-      </c>
-      <c r="B128" t="s">
-        <v>180</v>
-      </c>
-      <c r="C128" t="s">
-        <v>172</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F128" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F129" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G129" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B130" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B131" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D131">
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D132">
         <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F132" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C133" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D133">
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G133" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C134" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D134">
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F134" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D135">
         <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F135" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G135" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D136">
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D137">
         <v>3</v>
       </c>
       <c r="E137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F137" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D138">
         <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F138" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D139">
         <v>3</v>
       </c>
       <c r="E139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F139" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B140" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D140">
         <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F140" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B141" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D141">
         <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F141" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G141" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F142" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G142" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B143" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C143" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F143" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G143" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D144">
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F144" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G144" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B145" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C145" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D145">
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G145" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B146" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D146">
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F146" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G146" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B147" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D147">
         <v>3</v>
       </c>
       <c r="E147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F147" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G147" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B148" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D148">
         <v>3</v>
       </c>
       <c r="E148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F148" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G148" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
+        <v>175</v>
+      </c>
+      <c r="B149" t="s">
+        <v>179</v>
+      </c>
+      <c r="C149" t="s">
         <v>176</v>
-      </c>
-      <c r="B149" t="s">
-        <v>180</v>
-      </c>
-      <c r="C149" t="s">
-        <v>177</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F149" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07888178-D28B-4740-AB9E-A160790F907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="201">
   <si>
     <t>lang_code</t>
   </si>
@@ -57,6 +57,12 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>MyCountry</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
     <t>fra</t>
   </si>
   <si>
+    <t>Maroc</t>
+  </si>
+  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -78,6 +87,9 @@
     <t>Direction</t>
   </si>
   <si>
+    <t>MOR/NTH</t>
+  </si>
+  <si>
     <t>Nord</t>
   </si>
   <si>
@@ -90,6 +102,9 @@
     <t>Region</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK</t>
+  </si>
+  <si>
     <t>Rabat-Salé-Kénitra</t>
   </si>
   <si>
@@ -105,12 +120,18 @@
     <t>Province</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/RBT</t>
+  </si>
+  <si>
     <t>KTA</t>
   </si>
   <si>
     <t>Kenitra</t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/KTA</t>
+  </si>
+  <si>
     <t>Kénitra</t>
   </si>
   <si>
@@ -120,6 +141,9 @@
     <t>Salé </t>
   </si>
   <si>
+    <t>MOR/NTH/RSK/SAL</t>
+  </si>
+  <si>
     <t>Sala</t>
   </si>
   <si>
@@ -129,54 +153,81 @@
     <t>Casablanca-Settat</t>
   </si>
   <si>
+    <t>MOR/NTH/CST</t>
+  </si>
+  <si>
     <t>BSN</t>
   </si>
   <si>
     <t>Benslimane</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/BSN</t>
+  </si>
+  <si>
     <t>CSB</t>
   </si>
   <si>
     <t>Casablanca</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/CSB</t>
+  </si>
+  <si>
     <t>STT</t>
   </si>
   <si>
     <t>Settat</t>
   </si>
   <si>
+    <t>MOR/NTH/CST/STT</t>
+  </si>
+  <si>
     <t>ORT</t>
   </si>
   <si>
     <t>Oriental</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT</t>
+  </si>
+  <si>
     <t>NDR</t>
   </si>
   <si>
     <t>Nador</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/NDR</t>
+  </si>
+  <si>
     <t>BRK</t>
   </si>
   <si>
     <t>Berkane</t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/BRK</t>
+  </si>
+  <si>
     <t>JRD</t>
   </si>
   <si>
     <t>Jerada </t>
   </si>
   <si>
+    <t>MOR/NTH/ORT/JRD</t>
+  </si>
+  <si>
     <t>STH</t>
   </si>
   <si>
     <t>South</t>
   </si>
   <si>
+    <t>MOR/STH</t>
+  </si>
+  <si>
     <t>Sud</t>
   </si>
   <si>
@@ -186,24 +237,36 @@
     <t>Marrakesh-Safi</t>
   </si>
   <si>
+    <t>MOR/STH/MRS</t>
+  </si>
+  <si>
     <t>SAF</t>
   </si>
   <si>
     <t>Safi </t>
   </si>
   <si>
+    <t>MOR/STH/MRS/SAF</t>
+  </si>
+  <si>
     <t>YSF</t>
   </si>
   <si>
     <t>Youssoufia </t>
   </si>
   <si>
+    <t>MOR/STH/MRS/YSF</t>
+  </si>
+  <si>
     <t>SOS</t>
   </si>
   <si>
     <t>Souss-Massa</t>
   </si>
   <si>
+    <t>MOR/STH/SOS</t>
+  </si>
+  <si>
     <t>Sus-Massa</t>
   </si>
   <si>
@@ -213,12 +276,18 @@
     <t>Tata </t>
   </si>
   <si>
+    <t>MOR/STH/SOS/TTA</t>
+  </si>
+  <si>
     <t>TZT</t>
   </si>
   <si>
     <t>Tiznit</t>
   </si>
   <si>
+    <t>MOR/STH/SOS/TZT</t>
+  </si>
+  <si>
     <t>ara</t>
   </si>
   <si>
@@ -562,72 +631,6 @@
   </si>
   <si>
     <t>ប្រទេស</t>
-  </si>
-  <si>
-    <t>Utopia</t>
-  </si>
-  <si>
-    <t>UTO</t>
-  </si>
-  <si>
-    <t>UTO/NTH</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/RBT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/KTA</t>
-  </si>
-  <si>
-    <t>UTO/NTH/RSK/SAL</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/BSN</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/CSB</t>
-  </si>
-  <si>
-    <t>UTO/NTH/CST/STT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/NDR</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/BRK</t>
-  </si>
-  <si>
-    <t>UTO/NTH/ORT/JRD</t>
-  </si>
-  <si>
-    <t>UTO/STH</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS/SAF</t>
-  </si>
-  <si>
-    <t>UTO/STH/MRS/YSF</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS/TTA</t>
-  </si>
-  <si>
-    <t>UTO/STH/SOS/TZT</t>
   </si>
 </sst>
 </file>
@@ -1096,16 +1099,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.86328125" customWidth="1"/>
-    <col min="4" max="4" width="16.86328125" customWidth="1"/>
-    <col min="5" max="5" width="23.3984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.265625" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" style="2"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1131,3828 +1134,3828 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>179</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F42" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F50" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F51" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G51" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F53" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G53" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G54" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" t="s">
+        <v>51</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" t="s">
+        <v>51</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" t="s">
         <v>63</v>
       </c>
-      <c r="B55" t="s">
-        <v>41</v>
-      </c>
-      <c r="C55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>71</v>
-      </c>
-      <c r="F55" t="s">
-        <v>190</v>
-      </c>
-      <c r="G55" t="s">
-        <v>39</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56">
-        <v>3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" t="s">
-        <v>191</v>
-      </c>
-      <c r="G56" t="s">
-        <v>39</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" t="s">
-        <v>45</v>
-      </c>
-      <c r="C57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57">
-        <v>3</v>
-      </c>
-      <c r="E57" t="s">
-        <v>71</v>
-      </c>
-      <c r="F57" t="s">
-        <v>192</v>
-      </c>
-      <c r="G57" t="s">
-        <v>39</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" t="s">
-        <v>47</v>
-      </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
         <v>67</v>
       </c>
-      <c r="F58" t="s">
-        <v>193</v>
-      </c>
-      <c r="G58" t="s">
-        <v>179</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" t="s">
-        <v>50</v>
-      </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
+        <v>92</v>
+      </c>
+      <c r="F59" t="s">
         <v>69</v>
       </c>
-      <c r="F59" t="s">
-        <v>194</v>
-      </c>
       <c r="G59" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G60" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F61" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F62" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F63" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G63" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F64" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G64" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F66" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F67" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G67" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F68" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F69" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F70" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F71" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G71" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F72" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G72" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F73" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G73" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B74" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D74">
         <v>3</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F74" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G74" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F75" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G75" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D76">
         <v>3</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F76" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G76" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C77" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D77">
         <v>3</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F77" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G77" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F78" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G78" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F79" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G79" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C80" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F80" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G80" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>112</v>
       </c>
-      <c r="D81">
-        <v>3</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F81" t="s">
-        <v>195</v>
-      </c>
-      <c r="G81" t="s">
-        <v>50</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>89</v>
-      </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C82" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F82" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="D83">
         <v>2</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F83" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D84">
         <v>3</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F84" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G84" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="D85">
         <v>3</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F85" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F86" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="F87" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F88" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D89">
         <v>3</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F89" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D90">
         <v>3</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F90" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G90" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B91" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F91" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G91" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F92" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G92" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F93" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G93" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D94">
         <v>3</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F94" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G94" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D95">
         <v>3</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F95" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G95" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F96" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C97" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D97">
         <v>3</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F97" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G97" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D98">
         <v>3</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F98" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G98" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C99" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D99">
         <v>3</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F99" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G99" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C100" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F100" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G100" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B101" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D101">
         <v>2</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F101" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G101" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C102" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="D102">
         <v>3</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F102" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G102" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C103" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s">
+        <v>67</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>140</v>
       </c>
-      <c r="D103">
-        <v>3</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F103" t="s">
-        <v>196</v>
-      </c>
-      <c r="G103" t="s">
-        <v>50</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
-        <v>117</v>
-      </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C104" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F104" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G104" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C105" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D105">
         <v>3</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G105" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D106">
         <v>3</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F106" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G106" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="F107" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="F108" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G108" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F109" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G109" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B110" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C110" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="D110">
         <v>3</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F110" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C111" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="D111">
         <v>3</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G111" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D112">
         <v>3</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F112" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F113" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G113" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D114">
         <v>3</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F114" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G114" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C115" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D115">
         <v>3</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F115" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G115" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B116" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="D116">
         <v>3</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F116" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G116" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C117" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F117" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G117" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B118" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C118" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D118">
         <v>3</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F118" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G118" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B119" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C119" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D119">
         <v>3</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F119" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G119" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B120" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C120" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="D120">
         <v>3</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F120" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G120" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="F121" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G121" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B122" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F122" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G122" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B123" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C123" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D123">
         <v>3</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F123" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G123" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="D124">
         <v>3</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F124" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D125">
         <v>2</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F125" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G125" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B126" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C126" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="D126">
         <v>3</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F126" t="s">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G126" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B127" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D127">
         <v>3</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F127" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="G127" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B128" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F128" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C129" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="F129" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="G129" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F130" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="G130" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B131" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D131">
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F131" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B132" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D132">
         <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F132" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B133" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C133" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D133">
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F133" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B134" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C134" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D134">
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F134" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B135" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C135" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D135">
         <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F135" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G135" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C136" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D136">
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F136" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="G136" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B137" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C137" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D137">
         <v>3</v>
       </c>
       <c r="E137" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F137" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G137" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B138" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D138">
         <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F138" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="G138" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D139">
         <v>3</v>
       </c>
       <c r="E139" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F139" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="G139" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B140" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C140" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D140">
         <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F140" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="G140" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B141" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C141" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D141">
         <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F141" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="G141" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C142" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="F142" t="s">
+        <v>65</v>
+      </c>
+      <c r="G142" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>193</v>
       </c>
-      <c r="G142" t="s">
-        <v>179</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A143" t="s">
-        <v>170</v>
-      </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C143" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F143" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="G143" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B144" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D144">
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F144" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G144" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B145" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C145" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D145">
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F145" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>193</v>
+      </c>
+      <c r="B146" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" t="s">
         <v>196</v>
-      </c>
-      <c r="G145" t="s">
-        <v>50</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A146" t="s">
-        <v>170</v>
-      </c>
-      <c r="B146" t="s">
-        <v>56</v>
-      </c>
-      <c r="C146" t="s">
-        <v>173</v>
       </c>
       <c r="D146">
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F146" t="s">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>193</v>
+      </c>
+      <c r="B147" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" t="s">
         <v>197</v>
       </c>
-      <c r="G146" t="s">
-        <v>47</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A147" t="s">
-        <v>170</v>
-      </c>
-      <c r="B147" t="s">
-        <v>59</v>
-      </c>
-      <c r="C147" t="s">
-        <v>174</v>
-      </c>
       <c r="D147">
         <v>3</v>
       </c>
       <c r="E147" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F147" t="s">
+        <v>82</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>193</v>
+      </c>
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
+        <v>197</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="E148" t="s">
+        <v>197</v>
+      </c>
+      <c r="F148" t="s">
+        <v>85</v>
+      </c>
+      <c r="G148" t="s">
+        <v>76</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>198</v>
       </c>
-      <c r="G147" t="s">
-        <v>56</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A148" t="s">
-        <v>170</v>
-      </c>
-      <c r="B148" t="s">
-        <v>61</v>
-      </c>
-      <c r="C148" t="s">
-        <v>174</v>
-      </c>
-      <c r="D148">
-        <v>3</v>
-      </c>
-      <c r="E148" t="s">
-        <v>174</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="B149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" t="s">
         <v>199</v>
-      </c>
-      <c r="G148" t="s">
-        <v>56</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A149" t="s">
-        <v>175</v>
-      </c>
-      <c r="B149" t="s">
-        <v>179</v>
-      </c>
-      <c r="C149" t="s">
-        <v>176</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F149" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yash.mohan\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386A12A0-DB33-465B-99E9-90F94186CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B1103D-D50D-45AF-9452-4DF5B599A263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$149</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -96,9 +96,6 @@
     <t>RSK</t>
   </si>
   <si>
-    <t>RabatSaleKenitra</t>
-  </si>
-  <si>
     <t>Region</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   </si>
   <si>
     <t>ប្រទេស</t>
+  </si>
+  <si>
+    <t>Barnaby</t>
   </si>
 </sst>
 </file>
@@ -1098,17 +1098,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="2"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="4" max="4" width="16.86328125" customWidth="1"/>
+    <col min="5" max="5" width="23.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.265625" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1157,7 +1158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1240,16 +1241,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
       </c>
       <c r="G6" t="s">
         <v>16</v>
@@ -1258,7 +1259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1266,16 +1267,16 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
@@ -1284,24 +1285,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -1310,24 +1311,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
@@ -1336,24 +1337,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
       </c>
       <c r="G10" t="s">
         <v>21</v>
@@ -1362,24 +1363,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>21</v>
@@ -1388,24 +1389,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
         <v>36</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
       </c>
       <c r="G12" t="s">
         <v>21</v>
@@ -1414,24 +1415,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
         <v>21</v>
@@ -1440,24 +1441,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
@@ -1466,24 +1467,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
         <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
         <v>16</v>
@@ -1492,180 +1493,180 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
         <v>43</v>
       </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
         <v>43</v>
       </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
         <v>46</v>
       </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
         <v>45</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="s">
         <v>46</v>
       </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="s">
         <v>49</v>
       </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
         <v>49</v>
       </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
         <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G22" t="s">
         <v>16</v>
@@ -1674,24 +1675,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
         <v>51</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
@@ -1700,171 +1701,171 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
         <v>54</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" t="s">
         <v>55</v>
       </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>13</v>
       </c>
       <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
         <v>54</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
         <v>55</v>
       </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
         <v>57</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
         <v>58</v>
       </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
         <v>57</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" t="s">
         <v>58</v>
       </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
         <v>60</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" t="s">
         <v>61</v>
       </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
         <v>60</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" t="s">
         <v>61</v>
       </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
         <v>63</v>
-      </c>
-      <c r="C30" t="s">
-        <v>64</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1873,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
         <v>9</v>
@@ -1882,15 +1883,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1899,7 +1900,7 @@
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
@@ -1908,333 +1909,333 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
         <v>67</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
         <v>67</v>
-      </c>
-      <c r="C33" t="s">
-        <v>68</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
         <v>70</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" t="s">
         <v>71</v>
       </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" t="s">
-        <v>72</v>
-      </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
         <v>70</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" t="s">
         <v>71</v>
       </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" t="s">
-        <v>72</v>
-      </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
         <v>73</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
         <v>74</v>
       </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" t="s">
-        <v>75</v>
-      </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" t="s">
         <v>74</v>
       </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" t="s">
-        <v>75</v>
-      </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
         <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>77</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
         <v>80</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
         <v>81</v>
       </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" t="s">
-        <v>82</v>
-      </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>13</v>
       </c>
       <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" t="s">
         <v>80</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" t="s">
         <v>81</v>
       </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" t="s">
-        <v>82</v>
-      </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" t="s">
         <v>84</v>
       </c>
-      <c r="D42">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" t="s">
-        <v>85</v>
-      </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>13</v>
       </c>
       <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
         <v>83</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" t="s">
         <v>84</v>
       </c>
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
         <v>85</v>
-      </c>
-      <c r="G43" t="s">
-        <v>76</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>86</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
@@ -2243,21 +2244,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
@@ -2269,24 +2270,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
         <v>16</v>
@@ -2295,24 +2296,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
         <v>93</v>
       </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47" t="s">
-        <v>94</v>
-      </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G47" t="s">
         <v>21</v>
@@ -2321,24 +2322,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G48" t="s">
         <v>21</v>
@@ -2347,24 +2348,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s">
         <v>21</v>
@@ -2373,24 +2374,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G50" t="s">
         <v>16</v>
@@ -2399,102 +2400,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" t="s">
         <v>98</v>
       </c>
-      <c r="D51">
-        <v>3</v>
-      </c>
-      <c r="E51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F51" t="s">
-        <v>44</v>
-      </c>
-      <c r="G51" t="s">
-        <v>39</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>86</v>
-      </c>
-      <c r="B52" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" t="s">
         <v>99</v>
       </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52" t="s">
-        <v>94</v>
-      </c>
-      <c r="F52" t="s">
-        <v>47</v>
-      </c>
-      <c r="G52" t="s">
-        <v>39</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" t="s">
         <v>100</v>
-      </c>
-      <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" t="s">
-        <v>50</v>
-      </c>
-      <c r="G53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>86</v>
-      </c>
-      <c r="B54" t="s">
-        <v>51</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G54" t="s">
         <v>16</v>
@@ -2503,102 +2504,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" t="s">
+        <v>55</v>
+      </c>
+      <c r="G55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" t="s">
         <v>102</v>
       </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" t="s">
-        <v>56</v>
-      </c>
-      <c r="G55" t="s">
-        <v>51</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>86</v>
-      </c>
-      <c r="B56" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>58</v>
+      </c>
+      <c r="G56" t="s">
+        <v>50</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" t="s">
         <v>103</v>
       </c>
-      <c r="D56">
-        <v>3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-      <c r="G56" t="s">
-        <v>51</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" t="s">
         <v>104</v>
-      </c>
-      <c r="D57">
-        <v>3</v>
-      </c>
-      <c r="E57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" t="s">
-        <v>62</v>
-      </c>
-      <c r="G57" t="s">
-        <v>51</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" t="s">
-        <v>105</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G58" t="s">
         <v>9</v>
@@ -2607,177 +2608,177 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F59" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" t="s">
+        <v>62</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" t="s">
         <v>69</v>
       </c>
-      <c r="G59" t="s">
-        <v>63</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>86</v>
-      </c>
-      <c r="B60" t="s">
-        <v>70</v>
-      </c>
       <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" t="s">
+        <v>71</v>
+      </c>
+      <c r="G60" t="s">
+        <v>66</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" t="s">
         <v>107</v>
       </c>
-      <c r="D60">
-        <v>3</v>
-      </c>
-      <c r="E60" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" t="s">
-        <v>72</v>
-      </c>
-      <c r="G60" t="s">
-        <v>67</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s">
+        <v>66</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" t="s">
         <v>108</v>
-      </c>
-      <c r="D61">
-        <v>3</v>
-      </c>
-      <c r="E61" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" t="s">
-        <v>75</v>
-      </c>
-      <c r="G61" t="s">
-        <v>67</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>86</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" t="s">
-        <v>109</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" t="s">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" t="s">
         <v>110</v>
       </c>
-      <c r="D63">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" t="s">
-        <v>76</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
         <v>111</v>
-      </c>
-      <c r="D64">
-        <v>3</v>
-      </c>
-      <c r="E64" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" t="s">
-        <v>85</v>
-      </c>
-      <c r="G64" t="s">
-        <v>76</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>112</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -2786,21 +2787,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F66" t="s">
         <v>19</v>
@@ -2812,24 +2813,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
@@ -2838,24 +2839,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G68" t="s">
         <v>21</v>
@@ -2864,24 +2865,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G69" t="s">
         <v>21</v>
@@ -2890,24 +2891,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G70" t="s">
         <v>21</v>
@@ -2916,24 +2917,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -2942,102 +2943,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C72" t="s">
+        <v>124</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F72" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" t="s">
+        <v>38</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" t="s">
         <v>125</v>
       </c>
-      <c r="D72">
-        <v>3</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F72" t="s">
-        <v>44</v>
-      </c>
-      <c r="G72" t="s">
-        <v>39</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>112</v>
-      </c>
-      <c r="B73" t="s">
-        <v>45</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" t="s">
         <v>126</v>
       </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F73" t="s">
-        <v>47</v>
-      </c>
-      <c r="G73" t="s">
-        <v>39</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>112</v>
-      </c>
-      <c r="B74" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F74" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" t="s">
+        <v>38</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" t="s">
         <v>127</v>
-      </c>
-      <c r="D74">
-        <v>3</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F74" t="s">
-        <v>50</v>
-      </c>
-      <c r="G74" t="s">
-        <v>39</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>112</v>
-      </c>
-      <c r="B75" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" t="s">
-        <v>128</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
@@ -3046,102 +3047,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C76" t="s">
+        <v>128</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D76">
-        <v>3</v>
-      </c>
-      <c r="E76" s="10" t="s">
+      <c r="F76" t="s">
+        <v>55</v>
+      </c>
+      <c r="G76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>111</v>
+      </c>
+      <c r="B77" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" t="s">
         <v>130</v>
       </c>
-      <c r="F76" t="s">
-        <v>56</v>
-      </c>
-      <c r="G76" t="s">
-        <v>51</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>112</v>
-      </c>
-      <c r="B77" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" t="s">
+        <v>58</v>
+      </c>
+      <c r="G77" t="s">
+        <v>50</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C78" t="s">
         <v>131</v>
       </c>
-      <c r="D77">
-        <v>3</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F77" t="s">
-        <v>59</v>
-      </c>
-      <c r="G77" t="s">
-        <v>51</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>112</v>
-      </c>
-      <c r="B78" t="s">
-        <v>60</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" t="s">
         <v>132</v>
-      </c>
-      <c r="D78">
-        <v>3</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F78" t="s">
-        <v>62</v>
-      </c>
-      <c r="G78" t="s">
-        <v>51</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>112</v>
-      </c>
-      <c r="B79" t="s">
-        <v>63</v>
-      </c>
-      <c r="C79" t="s">
-        <v>133</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G79" t="s">
         <v>9</v>
@@ -3150,177 +3151,177 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F80" t="s">
+        <v>68</v>
+      </c>
+      <c r="G80" t="s">
+        <v>62</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" t="s">
         <v>69</v>
       </c>
-      <c r="G80" t="s">
-        <v>63</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B81" t="s">
-        <v>70</v>
-      </c>
       <c r="C81" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" t="s">
+        <v>71</v>
+      </c>
+      <c r="G81" t="s">
+        <v>66</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" t="s">
         <v>135</v>
       </c>
-      <c r="D81">
-        <v>3</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F81" t="s">
-        <v>72</v>
-      </c>
-      <c r="G81" t="s">
-        <v>67</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>112</v>
-      </c>
-      <c r="B82" t="s">
-        <v>73</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" t="s">
+        <v>74</v>
+      </c>
+      <c r="G82" t="s">
+        <v>66</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>111</v>
+      </c>
+      <c r="B83" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" t="s">
         <v>136</v>
-      </c>
-      <c r="D82">
-        <v>3</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F82" t="s">
-        <v>75</v>
-      </c>
-      <c r="G82" t="s">
-        <v>67</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>112</v>
-      </c>
-      <c r="B83" t="s">
-        <v>76</v>
-      </c>
-      <c r="C83" t="s">
-        <v>137</v>
       </c>
       <c r="D83">
         <v>2</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
+        <v>137</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F84" t="s">
+        <v>81</v>
+      </c>
+      <c r="G84" t="s">
+        <v>75</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" t="s">
+        <v>82</v>
+      </c>
+      <c r="C85" t="s">
         <v>138</v>
       </c>
-      <c r="D84">
-        <v>3</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F84" t="s">
-        <v>82</v>
-      </c>
-      <c r="G84" t="s">
-        <v>76</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G85" t="s">
+        <v>75</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
         <v>139</v>
-      </c>
-      <c r="D85">
-        <v>3</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F85" t="s">
-        <v>85</v>
-      </c>
-      <c r="G85" t="s">
-        <v>76</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>140</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -3329,21 +3330,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B87" t="s">
         <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F87" t="s">
         <v>19</v>
@@ -3355,24 +3356,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B88" t="s">
         <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
@@ -3381,24 +3382,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C89" t="s">
+        <v>146</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D89">
-        <v>3</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>148</v>
-      </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G89" t="s">
         <v>21</v>
@@ -3407,24 +3408,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D90">
         <v>3</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G90" t="s">
         <v>21</v>
@@ -3433,24 +3434,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G91" t="s">
         <v>21</v>
@@ -3459,24 +3460,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
@@ -3485,102 +3486,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C93" t="s">
+        <v>151</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
+        <v>38</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
         <v>152</v>
       </c>
-      <c r="D93">
-        <v>3</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F93" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" t="s">
-        <v>39</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>140</v>
-      </c>
-      <c r="B94" t="s">
-        <v>45</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F94" t="s">
+        <v>46</v>
+      </c>
+      <c r="G94" t="s">
+        <v>38</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" t="s">
+        <v>47</v>
+      </c>
+      <c r="C95" t="s">
         <v>153</v>
       </c>
-      <c r="D94">
-        <v>3</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F94" t="s">
-        <v>47</v>
-      </c>
-      <c r="G94" t="s">
-        <v>39</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>140</v>
-      </c>
-      <c r="B95" t="s">
-        <v>48</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="G95" t="s">
+        <v>38</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" t="s">
         <v>154</v>
-      </c>
-      <c r="D95">
-        <v>3</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F95" t="s">
-        <v>50</v>
-      </c>
-      <c r="G95" t="s">
-        <v>39</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>140</v>
-      </c>
-      <c r="B96" t="s">
-        <v>51</v>
-      </c>
-      <c r="C96" t="s">
-        <v>155</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G96" t="s">
         <v>16</v>
@@ -3589,102 +3590,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C97" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F97" t="s">
+        <v>55</v>
+      </c>
+      <c r="G97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" t="s">
         <v>156</v>
       </c>
-      <c r="D97">
-        <v>3</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F97" t="s">
-        <v>56</v>
-      </c>
-      <c r="G97" t="s">
-        <v>51</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>140</v>
-      </c>
-      <c r="B98" t="s">
-        <v>57</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F98" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" t="s">
+        <v>50</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" t="s">
+        <v>59</v>
+      </c>
+      <c r="C99" t="s">
         <v>157</v>
       </c>
-      <c r="D98">
-        <v>3</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F98" t="s">
-        <v>59</v>
-      </c>
-      <c r="G98" t="s">
-        <v>51</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>140</v>
-      </c>
-      <c r="B99" t="s">
-        <v>60</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="D99">
+        <v>3</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F99" t="s">
+        <v>61</v>
+      </c>
+      <c r="G99" t="s">
+        <v>50</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" t="s">
         <v>158</v>
-      </c>
-      <c r="D99">
-        <v>3</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F99" t="s">
-        <v>62</v>
-      </c>
-      <c r="G99" t="s">
-        <v>51</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>140</v>
-      </c>
-      <c r="B100" t="s">
-        <v>63</v>
-      </c>
-      <c r="C100" t="s">
-        <v>159</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G100" t="s">
         <v>9</v>
@@ -3693,177 +3694,177 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D101">
         <v>2</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F101" t="s">
+        <v>68</v>
+      </c>
+      <c r="G101" t="s">
+        <v>62</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>139</v>
+      </c>
+      <c r="B102" t="s">
         <v>69</v>
       </c>
-      <c r="G101" t="s">
-        <v>63</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>140</v>
-      </c>
-      <c r="B102" t="s">
-        <v>70</v>
-      </c>
       <c r="C102" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F102" t="s">
+        <v>71</v>
+      </c>
+      <c r="G102" t="s">
+        <v>66</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>139</v>
+      </c>
+      <c r="B103" t="s">
+        <v>72</v>
+      </c>
+      <c r="C103" t="s">
         <v>162</v>
       </c>
-      <c r="D102">
-        <v>3</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F102" t="s">
-        <v>72</v>
-      </c>
-      <c r="G102" t="s">
-        <v>67</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>140</v>
-      </c>
-      <c r="B103" t="s">
-        <v>73</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F103" t="s">
+        <v>74</v>
+      </c>
+      <c r="G103" t="s">
+        <v>66</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>139</v>
+      </c>
+      <c r="B104" t="s">
+        <v>75</v>
+      </c>
+      <c r="C104" t="s">
         <v>163</v>
-      </c>
-      <c r="D103">
-        <v>3</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F103" t="s">
-        <v>75</v>
-      </c>
-      <c r="G103" t="s">
-        <v>67</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>140</v>
-      </c>
-      <c r="B104" t="s">
-        <v>76</v>
-      </c>
-      <c r="C104" t="s">
-        <v>164</v>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C105" t="s">
+        <v>164</v>
+      </c>
+      <c r="D105">
+        <v>3</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F105" t="s">
+        <v>81</v>
+      </c>
+      <c r="G105" t="s">
+        <v>75</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>139</v>
+      </c>
+      <c r="B106" t="s">
+        <v>82</v>
+      </c>
+      <c r="C106" t="s">
         <v>165</v>
       </c>
-      <c r="D105">
-        <v>3</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F105" t="s">
-        <v>82</v>
-      </c>
-      <c r="G105" t="s">
-        <v>76</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>140</v>
-      </c>
-      <c r="B106" t="s">
-        <v>83</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="D106">
+        <v>3</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F106" t="s">
+        <v>84</v>
+      </c>
+      <c r="G106" t="s">
+        <v>75</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
         <v>166</v>
-      </c>
-      <c r="D106">
-        <v>3</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F106" t="s">
-        <v>85</v>
-      </c>
-      <c r="G106" t="s">
-        <v>76</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>167</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F107" t="s">
         <v>9</v>
@@ -3872,21 +3873,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B108" t="s">
         <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108" t="s">
         <v>19</v>
@@ -3898,24 +3899,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B109" t="s">
         <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F109" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G109" t="s">
         <v>16</v>
@@ -3924,24 +3925,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C110" t="s">
+        <v>173</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D110">
-        <v>3</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>175</v>
-      </c>
       <c r="F110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G110" t="s">
         <v>21</v>
@@ -3950,24 +3951,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C111" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D111">
         <v>3</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G111" t="s">
         <v>21</v>
@@ -3976,24 +3977,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C112" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D112">
         <v>3</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F112" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G112" t="s">
         <v>21</v>
@@ -4002,24 +4003,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C113" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
@@ -4028,102 +4029,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C114" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114">
+        <v>3</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F114" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114" t="s">
+        <v>38</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>166</v>
+      </c>
+      <c r="B115" t="s">
+        <v>44</v>
+      </c>
+      <c r="C115" t="s">
         <v>179</v>
       </c>
-      <c r="D114">
-        <v>3</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F114" t="s">
-        <v>44</v>
-      </c>
-      <c r="G114" t="s">
-        <v>39</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>167</v>
-      </c>
-      <c r="B115" t="s">
-        <v>45</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="D115">
+        <v>3</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F115" t="s">
+        <v>46</v>
+      </c>
+      <c r="G115" t="s">
+        <v>38</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>166</v>
+      </c>
+      <c r="B116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" t="s">
         <v>180</v>
       </c>
-      <c r="D115">
-        <v>3</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F115" t="s">
-        <v>47</v>
-      </c>
-      <c r="G115" t="s">
-        <v>39</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>167</v>
-      </c>
-      <c r="B116" t="s">
-        <v>48</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="D116">
+        <v>3</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F116" t="s">
+        <v>49</v>
+      </c>
+      <c r="G116" t="s">
+        <v>38</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>166</v>
+      </c>
+      <c r="B117" t="s">
+        <v>50</v>
+      </c>
+      <c r="C117" t="s">
         <v>181</v>
-      </c>
-      <c r="D116">
-        <v>3</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F116" t="s">
-        <v>50</v>
-      </c>
-      <c r="G116" t="s">
-        <v>39</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>167</v>
-      </c>
-      <c r="B117" t="s">
-        <v>51</v>
-      </c>
-      <c r="C117" t="s">
-        <v>182</v>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G117" t="s">
         <v>16</v>
@@ -4132,102 +4133,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C118" t="s">
+        <v>182</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F118" t="s">
+        <v>55</v>
+      </c>
+      <c r="G118" t="s">
+        <v>50</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" t="s">
         <v>183</v>
       </c>
-      <c r="D118">
-        <v>3</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F118" t="s">
-        <v>56</v>
-      </c>
-      <c r="G118" t="s">
-        <v>51</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>167</v>
-      </c>
-      <c r="B119" t="s">
-        <v>57</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="D119">
+        <v>3</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F119" t="s">
+        <v>58</v>
+      </c>
+      <c r="G119" t="s">
+        <v>50</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>166</v>
+      </c>
+      <c r="B120" t="s">
+        <v>59</v>
+      </c>
+      <c r="C120" t="s">
         <v>184</v>
       </c>
-      <c r="D119">
-        <v>3</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F119" t="s">
-        <v>59</v>
-      </c>
-      <c r="G119" t="s">
-        <v>51</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>167</v>
-      </c>
-      <c r="B120" t="s">
-        <v>60</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="D120">
+        <v>3</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F120" t="s">
+        <v>61</v>
+      </c>
+      <c r="G120" t="s">
+        <v>50</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>166</v>
+      </c>
+      <c r="B121" t="s">
+        <v>62</v>
+      </c>
+      <c r="C121" t="s">
         <v>185</v>
-      </c>
-      <c r="D120">
-        <v>3</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F120" t="s">
-        <v>62</v>
-      </c>
-      <c r="G120" t="s">
-        <v>51</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>167</v>
-      </c>
-      <c r="B121" t="s">
-        <v>63</v>
-      </c>
-      <c r="C121" t="s">
-        <v>186</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G121" t="s">
         <v>9</v>
@@ -4236,177 +4237,177 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F122" t="s">
+        <v>68</v>
+      </c>
+      <c r="G122" t="s">
+        <v>62</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>166</v>
+      </c>
+      <c r="B123" t="s">
         <v>69</v>
       </c>
-      <c r="G122" t="s">
-        <v>63</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>167</v>
-      </c>
-      <c r="B123" t="s">
-        <v>70</v>
-      </c>
       <c r="C123" t="s">
+        <v>187</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F123" t="s">
+        <v>71</v>
+      </c>
+      <c r="G123" t="s">
+        <v>66</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>166</v>
+      </c>
+      <c r="B124" t="s">
+        <v>72</v>
+      </c>
+      <c r="C124" t="s">
         <v>188</v>
       </c>
-      <c r="D123">
-        <v>3</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F123" t="s">
-        <v>72</v>
-      </c>
-      <c r="G123" t="s">
-        <v>67</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>167</v>
-      </c>
-      <c r="B124" t="s">
-        <v>73</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F124" t="s">
+        <v>74</v>
+      </c>
+      <c r="G124" t="s">
+        <v>66</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>166</v>
+      </c>
+      <c r="B125" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" t="s">
         <v>189</v>
-      </c>
-      <c r="D124">
-        <v>3</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F124" t="s">
-        <v>75</v>
-      </c>
-      <c r="G124" t="s">
-        <v>67</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>167</v>
-      </c>
-      <c r="B125" t="s">
-        <v>76</v>
-      </c>
-      <c r="C125" t="s">
-        <v>190</v>
       </c>
       <c r="D125">
         <v>2</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F125" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G125" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C126" t="s">
+        <v>190</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F126" t="s">
+        <v>81</v>
+      </c>
+      <c r="G126" t="s">
+        <v>75</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>166</v>
+      </c>
+      <c r="B127" t="s">
+        <v>82</v>
+      </c>
+      <c r="C127" t="s">
         <v>191</v>
       </c>
-      <c r="D126">
-        <v>3</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F126" t="s">
-        <v>82</v>
-      </c>
-      <c r="G126" t="s">
-        <v>76</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>167</v>
-      </c>
-      <c r="B127" t="s">
-        <v>83</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F127" t="s">
+        <v>84</v>
+      </c>
+      <c r="G127" t="s">
+        <v>75</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
         <v>192</v>
-      </c>
-      <c r="D127">
-        <v>3</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F127" t="s">
-        <v>85</v>
-      </c>
-      <c r="G127" t="s">
-        <v>76</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>193</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F128" t="s">
         <v>9</v>
@@ -4415,21 +4416,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B129" t="s">
         <v>16</v>
       </c>
       <c r="C129" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
@@ -4441,24 +4442,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B130" t="s">
         <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G130" t="s">
         <v>16</v>
@@ -4467,24 +4468,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B131" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D131">
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G131" t="s">
         <v>21</v>
@@ -4493,24 +4494,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D132">
         <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G132" t="s">
         <v>21</v>
@@ -4519,24 +4520,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C133" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D133">
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G133" t="s">
         <v>21</v>
@@ -4545,24 +4546,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C134" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D134">
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G134" t="s">
         <v>16</v>
@@ -4571,102 +4572,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D135">
         <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F135" t="s">
+        <v>43</v>
+      </c>
+      <c r="G135" t="s">
+        <v>38</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>192</v>
+      </c>
+      <c r="B136" t="s">
         <v>44</v>
       </c>
-      <c r="G135" t="s">
-        <v>39</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>193</v>
-      </c>
-      <c r="B136" t="s">
-        <v>45</v>
-      </c>
       <c r="C136" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D136">
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F136" t="s">
+        <v>46</v>
+      </c>
+      <c r="G136" t="s">
+        <v>38</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>192</v>
+      </c>
+      <c r="B137" t="s">
         <v>47</v>
       </c>
-      <c r="G136" t="s">
-        <v>39</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>193</v>
-      </c>
-      <c r="B137" t="s">
-        <v>48</v>
-      </c>
       <c r="C137" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D137">
         <v>3</v>
       </c>
       <c r="E137" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F137" t="s">
+        <v>49</v>
+      </c>
+      <c r="G137" t="s">
+        <v>38</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>192</v>
+      </c>
+      <c r="B138" t="s">
         <v>50</v>
       </c>
-      <c r="G137" t="s">
-        <v>39</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>193</v>
-      </c>
-      <c r="B138" t="s">
-        <v>51</v>
-      </c>
       <c r="C138" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D138">
         <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F138" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G138" t="s">
         <v>16</v>
@@ -4675,102 +4676,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C139" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D139">
         <v>3</v>
       </c>
       <c r="E139" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F139" t="s">
+        <v>55</v>
+      </c>
+      <c r="G139" t="s">
+        <v>50</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>192</v>
+      </c>
+      <c r="B140" t="s">
         <v>56</v>
       </c>
-      <c r="G139" t="s">
-        <v>51</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>193</v>
-      </c>
-      <c r="B140" t="s">
-        <v>57</v>
-      </c>
       <c r="C140" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D140">
         <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F140" t="s">
+        <v>58</v>
+      </c>
+      <c r="G140" t="s">
+        <v>50</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>192</v>
+      </c>
+      <c r="B141" t="s">
         <v>59</v>
       </c>
-      <c r="G140" t="s">
-        <v>51</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>193</v>
-      </c>
-      <c r="B141" t="s">
-        <v>60</v>
-      </c>
       <c r="C141" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D141">
         <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F141" t="s">
+        <v>61</v>
+      </c>
+      <c r="G141" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>192</v>
+      </c>
+      <c r="B142" t="s">
         <v>62</v>
       </c>
-      <c r="G141" t="s">
-        <v>51</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>193</v>
-      </c>
-      <c r="B142" t="s">
-        <v>63</v>
-      </c>
       <c r="C142" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F142" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G142" t="s">
         <v>9</v>
@@ -4779,177 +4780,177 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C143" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
+        <v>195</v>
+      </c>
+      <c r="F143" t="s">
+        <v>68</v>
+      </c>
+      <c r="G143" t="s">
+        <v>62</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>192</v>
+      </c>
+      <c r="B144" t="s">
+        <v>69</v>
+      </c>
+      <c r="C144" t="s">
         <v>196</v>
       </c>
-      <c r="F143" t="s">
-        <v>69</v>
-      </c>
-      <c r="G143" t="s">
-        <v>63</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>193</v>
-      </c>
-      <c r="B144" t="s">
-        <v>70</v>
-      </c>
-      <c r="C144" t="s">
-        <v>197</v>
-      </c>
       <c r="D144">
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F144" t="s">
+        <v>71</v>
+      </c>
+      <c r="G144" t="s">
+        <v>66</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>192</v>
+      </c>
+      <c r="B145" t="s">
         <v>72</v>
       </c>
-      <c r="G144" t="s">
-        <v>67</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>193</v>
-      </c>
-      <c r="B145" t="s">
-        <v>73</v>
-      </c>
       <c r="C145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D145">
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F145" t="s">
+        <v>74</v>
+      </c>
+      <c r="G145" t="s">
+        <v>66</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>192</v>
+      </c>
+      <c r="B146" t="s">
         <v>75</v>
       </c>
-      <c r="G145" t="s">
-        <v>67</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>193</v>
-      </c>
-      <c r="B146" t="s">
-        <v>76</v>
-      </c>
       <c r="C146" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D146">
         <v>2</v>
       </c>
       <c r="E146" t="s">
+        <v>195</v>
+      </c>
+      <c r="F146" t="s">
+        <v>77</v>
+      </c>
+      <c r="G146" t="s">
+        <v>62</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>192</v>
+      </c>
+      <c r="B147" t="s">
+        <v>79</v>
+      </c>
+      <c r="C147" t="s">
         <v>196</v>
       </c>
-      <c r="F146" t="s">
-        <v>78</v>
-      </c>
-      <c r="G146" t="s">
-        <v>63</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>193</v>
-      </c>
-      <c r="B147" t="s">
-        <v>80</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D147">
+        <v>3</v>
+      </c>
+      <c r="E147" t="s">
+        <v>196</v>
+      </c>
+      <c r="F147" t="s">
+        <v>81</v>
+      </c>
+      <c r="G147" t="s">
+        <v>75</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>192</v>
+      </c>
+      <c r="B148" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" t="s">
+        <v>196</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="E148" t="s">
+        <v>196</v>
+      </c>
+      <c r="F148" t="s">
+        <v>84</v>
+      </c>
+      <c r="G148" t="s">
+        <v>75</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
         <v>197</v>
-      </c>
-      <c r="D147">
-        <v>3</v>
-      </c>
-      <c r="E147" t="s">
-        <v>197</v>
-      </c>
-      <c r="F147" t="s">
-        <v>82</v>
-      </c>
-      <c r="G147" t="s">
-        <v>76</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>193</v>
-      </c>
-      <c r="B148" t="s">
-        <v>83</v>
-      </c>
-      <c r="C148" t="s">
-        <v>197</v>
-      </c>
-      <c r="D148">
-        <v>3</v>
-      </c>
-      <c r="E148" t="s">
-        <v>197</v>
-      </c>
-      <c r="F148" t="s">
-        <v>85</v>
-      </c>
-      <c r="G148" t="s">
-        <v>76</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>198</v>
       </c>
       <c r="B149" t="s">
         <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F149" t="s">
         <v>9</v>
@@ -4959,7 +4960,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H149" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="RSK"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
